--- a/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
+++ b/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
@@ -1,373 +1,340 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Respostas ao formulário 1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="239">
-  <si>
-    <t>Carimbo de data/hora</t>
-  </si>
-  <si>
-    <t>Identification of analysts</t>
-  </si>
-  <si>
-    <t>Which region is being analyzed?</t>
-  </si>
-  <si>
-    <t>Which platform is being analyzed?</t>
-  </si>
-  <si>
-    <t>SC1: Does the platform offer an API for collecting public user-generated content data?
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="238">
+  <si>
+    <t xml:space="preserve">Carimbo de data/hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification of analysts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which region is being analyzed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which platform is being analyzed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC1: Does the platform offer an API for collecting public user-generated content data?
 This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration.</t>
   </si>
   <si>
-    <t>SC1: Justification</t>
-  </si>
-  <si>
-    <t>SC2: Can the full scope of public content data be extracted through the platform’s API?
+    <t xml:space="preserve">SC1: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC2: Can the full scope of public content data be extracted through the platform’s API?
 This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness.</t>
   </si>
   <si>
-    <t>SC2: Justification</t>
-  </si>
-  <si>
-    <t>SC3: Is access to the platform’s API free of charge?
+    <t xml:space="preserve">SC2: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3: Is access to the platform’s API free of charge?
 This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access.</t>
   </si>
   <si>
-    <t>SC3: Justification</t>
-  </si>
-  <si>
-    <t>SC4: Does the platform offer a graphical interface for extracting data?
+    <t xml:space="preserve">SC3: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC4: Does the platform offer a graphical interface for extracting data?
 This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming.</t>
   </si>
   <si>
-    <t>SC4: Justification</t>
-  </si>
-  <si>
-    <t>OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
+    <t xml:space="preserve">SC4: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
 This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms.</t>
   </si>
   <si>
-    <t>OC1: Justification</t>
-  </si>
-  <si>
-    <t>OC2: Can the requested data be extracted directly from the platform’s API response?
+    <t xml:space="preserve">OC1: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC2: Can the requested data be extracted directly from the platform’s API response?
 This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself.</t>
   </si>
   <si>
-    <t>OC2: Justification</t>
-  </si>
-  <si>
-    <t>OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
+    <t xml:space="preserve">OC2: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
 This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access.</t>
   </si>
   <si>
-    <t>OC3: Justification</t>
-  </si>
-  <si>
-    <t>OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
+    <t xml:space="preserve">OC3: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
 This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier.</t>
   </si>
   <si>
-    <t>OC4: Justification</t>
-  </si>
-  <si>
-    <t>OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
+    <t xml:space="preserve">OC4: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
 This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author.</t>
   </si>
   <si>
-    <t>OC5: Justification</t>
-  </si>
-  <si>
-    <t>OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
+    <t xml:space="preserve">OC5: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
 This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts.</t>
   </si>
   <si>
-    <t>OC6: Justification</t>
-  </si>
-  <si>
-    <t>OC7: Does the API use locale-neutral data representations?
+    <t xml:space="preserve">OC6: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC7: Does the API use locale-neutral data representations?
 This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata.</t>
   </si>
   <si>
-    <t>OC7: Justification</t>
-  </si>
-  <si>
-    <t>OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
+    <t xml:space="preserve">OC7: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
 This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features.</t>
   </si>
   <si>
-    <t>OC8: Justification</t>
-  </si>
-  <si>
-    <t>OC9: Is the platform’s API documentation published in open access?
+    <t xml:space="preserve">OC8: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC9: Is the platform’s API documentation published in open access?
 This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication.</t>
   </si>
   <si>
-    <t>OC9: Justification</t>
-  </si>
-  <si>
-    <t>OC10: Is the platform’s API documentation clearly written and exemplified?
+    <t xml:space="preserve">OC9: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC10: Is the platform’s API documentation clearly written and exemplified?
 This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage.</t>
   </si>
   <si>
-    <t>OC10: Justification</t>
-  </si>
-  <si>
-    <t>OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
+    <t xml:space="preserve">OC10: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
 This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access.</t>
   </si>
   <si>
-    <t>OC11: Justification</t>
-  </si>
-  <si>
-    <t>OC12: Does the platform’s API documentation detail the response format of each endpoint?
+    <t xml:space="preserve">OC11: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC12: Does the platform’s API documentation detail the response format of each endpoint?
 This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs.</t>
   </si>
   <si>
-    <t>OC12: Justification</t>
-  </si>
-  <si>
-    <t>OC13: Does the platform provide its API documentation in the official languages of the assessed region?
+    <t xml:space="preserve">OC12: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC13: Does the platform provide its API documentation in the official languages of the assessed region?
 This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages.</t>
   </si>
   <si>
-    <t>OC13: Justification</t>
-  </si>
-  <si>
-    <t>OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
+    <t xml:space="preserve">OC13: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
 This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type.</t>
   </si>
   <si>
-    <t>OC14: Justification</t>
+    <t xml:space="preserve">OC14: Justification</t>
   </si>
   <si>
     <t xml:space="preserve">OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?
 This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. </t>
   </si>
   <si>
-    <t>OC15: Justification</t>
-  </si>
-  <si>
-    <t>OC16: Can data from a publication’s comments be extracted using the platform’s API?
+    <t xml:space="preserve">OC15: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC16: Can data from a publication’s comments be extracted using the platform’s API?
 This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features.</t>
   </si>
   <si>
-    <t>OC16: Justification</t>
-  </si>
-  <si>
-    <t>OC17: Can data from temporary content be extracted through the platform’s API?
+    <t xml:space="preserve">OC16: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC17: Can data from temporary content be extracted through the platform’s API?
 This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features.</t>
   </si>
   <si>
-    <t>OC17: Justification</t>
-  </si>
-  <si>
-    <t>OC18: Can historical data be extracted through the platform’s API?
+    <t xml:space="preserve">OC17: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC18: Can historical data be extracted through the platform’s API?
 This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved.</t>
   </si>
   <si>
-    <t>OC18: Justification</t>
-  </si>
-  <si>
-    <t>OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
+    <t xml:space="preserve">OC18: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
 This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously.</t>
   </si>
   <si>
-    <t>OC19: Justification</t>
-  </si>
-  <si>
-    <t>OC20: Are the results returned by the API consistently reproducible?
+    <t xml:space="preserve">OC19: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC20: Are the results returned by the API consistently reproducible?
 This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly, including content that has been deleted between collections. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
   </si>
   <si>
-    <t>OC20: Justification</t>
-  </si>
-  <si>
-    <t>OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
+    <t xml:space="preserve">OC20: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
 This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
   </si>
   <si>
-    <t>OC21: Justification</t>
-  </si>
-  <si>
-    <t>OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
+    <t xml:space="preserve">OC21: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
 This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented.</t>
   </si>
   <si>
-    <t>OC22: Justification</t>
-  </si>
-  <si>
-    <t>OC23: Does the platform’s API allow for filtering data based on publisher location?
+    <t xml:space="preserve">OC22: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC23: Does the platform’s API allow for filtering data based on publisher location?
 This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location.</t>
   </si>
   <si>
-    <t>OC23: Justification</t>
-  </si>
-  <si>
-    <t>OC24: Does the platform’s API allow for filtering data based on content language?
+    <t xml:space="preserve">OC23: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC24: Does the platform’s API allow for filtering data based on content language?
 This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language.</t>
   </si>
   <si>
-    <t>OC24: Justification</t>
-  </si>
-  <si>
-    <t>OC25: Does the platform’s API allow for filtering data by specific time periods?
+    <t xml:space="preserve">OC24: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC25: Does the platform’s API allow for filtering data by specific time periods?
 This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges.</t>
   </si>
   <si>
-    <t>OC25: Justification</t>
-  </si>
-  <si>
-    <t>OC26: Can data from newly published content be extracted from the platform’s API in near real time?
+    <t xml:space="preserve">OC25: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC26: Can data from newly published content be extracted from the platform’s API in near real time?
 This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data.</t>
   </si>
   <si>
-    <t>OC26: Justification</t>
-  </si>
-  <si>
-    <t>João Gabriel Haddad and Vinicius Branco</t>
-  </si>
-  <si>
-    <t>LinkedIn</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>No or not applicable</t>
-  </si>
-  <si>
-    <t>Danielle Mello and João Gabriel Haddad</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
-https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
-    </r>
-  </si>
-  <si>
-    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
+    <t xml:space="preserve">OC26: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Gabriel Haddad and Vinicius Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No or not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Mello and João Gabriel Haddad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t>Yes, but only for approved researchers</t>
-  </si>
-  <si>
-    <t>Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
-    </r>
-  </si>
-  <si>
-    <t>João Haddad e Vinicius Scortegagna</t>
-  </si>
-  <si>
-    <t>Bluesky</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
+https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, but only for approved researchers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Haddad e Vinicius Scortegagna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluesky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
   </si>
   <si>
     <t xml:space="preserve">All public content data can be extracted through the API. </t>
   </si>
   <si>
-    <t>The platforms requires only a BlueSky account to access the API</t>
-  </si>
-  <si>
-    <t>The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">This question is not applicable for Bluesky, because:
+    <t xml:space="preserve">The platforms requires only a BlueSky account to access the API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This question is not applicable for Bluesky, because:
 * There is no specific authentication for researchers.
 * There is no private accounts or posts at Bluesky
 * There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.
 Source: 
 https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF434343"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://atproto.blue/en/latest/dm.html</t>
-    </r>
-  </si>
-  <si>
-    <t>Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
-  </si>
-  <si>
-    <t>Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
+https://atproto.blue/en/latest/dm.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an endpoint for extrating data from an individual publication. </t>
@@ -383,45 +350,35 @@
 </t>
   </si>
   <si>
-    <t>We did not find a change log in official API documentation, only reference for a change log from a developer</t>
-  </si>
-  <si>
-    <t>It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
-  </si>
-  <si>
-    <t>The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://docs.bsky.app/docs/support/developer-guidelines</t>
-    </r>
-  </si>
-  <si>
-    <t>There is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
-  </si>
-  <si>
-    <t>The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t>The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t>The Bluesky API only provides a way to a post author self-label the post content. 
+    <t xml:space="preserve">We did not find a change log in official API documentation, only reference for a change log from a developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bluesky API only provides a way to a post author self-label the post content. 
 * Check [SelfLabel definition](https://atproto.blue/en/latest/atproto/atproto_client.models.com.atproto.label.defs.html#atproto_client.models.com.atproto.label.defs.SelfLabel). However, there is no specific label for AI-generated content.</t>
   </si>
   <si>
-    <t>Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t>Bluesky does not have temporary content features.</t>
+    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluesky does not have temporary content features.</t>
   </si>
   <si>
     <t xml:space="preserve">It is possible to extract historical data through the API. </t>
@@ -451,139 +408,125 @@
     <t xml:space="preserve">Data can be extrated in near real time in Bluesky. </t>
   </si>
   <si>
-    <t>Fernando Ferreira &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>WhatsApp</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>TikTok</t>
-  </si>
-  <si>
-    <t>TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
-  </si>
-  <si>
-    <t>TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
-  </si>
-  <si>
-    <t>Rafael Tadeu &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>Kwai</t>
-  </si>
-  <si>
-    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>Danielle and Adriano</t>
-  </si>
-  <si>
-    <t>Snapchat</t>
-  </si>
-  <si>
-    <t>Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
+    <t xml:space="preserve">Fernando Ferreira &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Tadeu &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle and Adriano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapchat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
 Source: https://developers.snap.com/api/home https://developers.snap.com/api/marketing-api/Public-Profile-API/GetStarted https://developers.snap.com/api/marketing-api/Public-Profile-API/CreatorDiscovery</t>
   </si>
   <si>
-    <t>Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t xml:space="preserve">Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t xml:space="preserve">The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
-  </si>
-  <si>
-    <t>The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
+    <t xml:space="preserve">Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
-  </si>
-  <si>
-    <t>Felipe Grael &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>Discord</t>
-  </si>
-  <si>
-    <t>The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
-  </si>
-  <si>
-    <t>Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>João Gabriel Haddad &amp; Vinícius Branco</t>
-  </si>
-  <si>
-    <t>Pinterest</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/</t>
-    </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve"> and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
-    </r>
-  </si>
-  <si>
-    <t>Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Adriano Belisario e Lucas Murakami</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
+    <t xml:space="preserve">Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe Grael &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Gabriel Haddad &amp; Vinícius Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriano Belisario e Lucas Murakami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
 https://developers.google.com/youtube/v3/docs.</t>
   </si>
   <si>
@@ -642,19 +585,9 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
+    <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
 https://developers.google.com/youtube/v3/docs 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://developers.google.com/youtube/terms</t>
-    </r>
+https://developers.google.com/youtube/terms</t>
   </si>
   <si>
     <t xml:space="preserve">Each method in the YouTube Data API v3 includes an example of its response format.
@@ -698,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
+    <t xml:space="preserve">The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
   </si>
   <si>
     <t xml:space="preserve">The documentation does not guarantee that API results are consistently reproducible and explicitly acknowledges approximations in key metrics. We made the same request to the search list endpoint multiple times, using “relevance” for the order parameter. The results differed in the order of the returned items. Additionally, after deletion, YouTube videos and comments cannot be queried. 
@@ -712,7 +645,7 @@
 </t>
   </si>
   <si>
-    <t>We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
+    <t xml:space="preserve">We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
   </si>
   <si>
     <t xml:space="preserve">The API does not support filtering by channel/publisher location. This feature was deprecated from API v2. Currently, the “search.list” endpoint includes a location parameter, but this applies to video geographic metadata (where content was filmed), not channel/publisher location. The “regionCode” parameter "instructs the API to return search results for videos that can be viewed in the specified country", filtering by content availability region, not by publishers’ location.
@@ -735,94 +668,94 @@
 </t>
   </si>
   <si>
-    <t>X/Twitter</t>
-  </si>
-  <si>
-    <t>X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
-  </si>
-  <si>
-    <t>Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
-  </si>
-  <si>
-    <t>In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
-  </si>
-  <si>
-    <t>X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
-  </si>
-  <si>
-    <t>If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
-  </si>
-  <si>
-    <t>The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
-  </si>
-  <si>
-    <t>Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
-  </si>
-  <si>
-    <t>For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
-  </si>
-  <si>
-    <t>The API documentation is available only in English (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t>X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
-  </si>
-  <si>
-    <t>Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t>The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
-  </si>
-  <si>
-    <t>Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
-  </si>
-  <si>
-    <t>Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t>Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
-  </si>
-  <si>
-    <t>The platform returns data which matches the parameters and filters applied.</t>
-  </si>
-  <si>
-    <t>The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
-  </si>
-  <si>
-    <t>The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
-  </si>
-  <si>
-    <t>In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
-  </si>
-  <si>
-    <t>Telegram</t>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The API documentation is available only in English (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform returns data which matches the parameters and filters applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telegram</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an API that allows the collection of public data in Telegram conversations.
@@ -836,10 +769,10 @@
 </t>
   </si>
   <si>
-    <t>All Telegram APIs are free of charge: https://core.telegram.org/</t>
-  </si>
-  <si>
-    <t>Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
+    <t xml:space="preserve">All Telegram APIs are free of charge: https://core.telegram.org/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram API access requires an access key that remains the same even after logging in multiple times. It will only change in specific situations, and the API provides the necessary methods to update it programmatically.
@@ -875,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
+    <t xml:space="preserve">Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
   </si>
   <si>
     <t xml:space="preserve">The Telegram and TDLib API documentation is not clearly written or exemplified. While it provides a technical reference of available classes and methods, it lacks detailed explanations and practical examples demonstrating how to call endpoints or implement typical workflows. The documentation’s structure assumes prior familiarity with Telegram’s internal architecture, making it difficult for developers to understand usage without relying on third-party resources or community libraries.
@@ -903,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
+    <t xml:space="preserve">We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram allows extracting comments from channels with discussion features enabled. Each comment is treated as a reply within a message thread, which can be retrieved as structured data.
@@ -937,7 +870,7 @@
 </t>
   </si>
   <si>
-    <t>Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
+    <t xml:space="preserve">Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram’s TDLib and core API do not include any parameters or methods that enable filtering data based on the language of message content.
@@ -959,31 +892,48 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-      <name val="Roboto"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -991,470 +941,263 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FF3D3D3D"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
+          <fgColor rgb="FF0000FF"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Respostas ao formulário 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BL14" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BL14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="64">
-    <tableColumn name="Carimbo de data/hora" id="1"/>
-    <tableColumn name="Identification of analysts" id="2"/>
-    <tableColumn name="Which region is being analyzed?" id="3"/>
-    <tableColumn name="Which platform is being analyzed?" id="4"/>
-    <tableColumn name="SC1: Does the platform offer an API for collecting public user-generated content data?_x000a_This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration." id="5"/>
-    <tableColumn name="SC1: Justification" id="6"/>
-    <tableColumn name="SC2: Can the full scope of public content data be extracted through the platform’s API?_x000a_This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness." id="7"/>
-    <tableColumn name="SC2: Justification" id="8"/>
-    <tableColumn name="SC3: Is access to the platform’s API free of charge?_x000a_This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access." id="9"/>
-    <tableColumn name="SC3: Justification" id="10"/>
-    <tableColumn name="SC4: Does the platform offer a graphical interface for extracting data?_x000a_This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming." id="11"/>
-    <tableColumn name="SC4: Justification" id="12"/>
-    <tableColumn name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?_x000a_This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms." id="13"/>
-    <tableColumn name="OC1: Justification" id="14"/>
-    <tableColumn name="OC2: Can the requested data be extracted directly from the platform’s API response?_x000a_This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself." id="15"/>
-    <tableColumn name="OC2: Justification" id="16"/>
-    <tableColumn name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?_x000a_This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access." id="17"/>
-    <tableColumn name="OC3: Justification" id="18"/>
-    <tableColumn name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?_x000a_This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier." id="19"/>
-    <tableColumn name="OC4: Justification" id="20"/>
-    <tableColumn name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?_x000a_This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author." id="21"/>
-    <tableColumn name="OC5: Justification" id="22"/>
-    <tableColumn name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?_x000a_This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts." id="23"/>
-    <tableColumn name="OC6: Justification" id="24"/>
-    <tableColumn name="OC7: Does the API use locale-neutral data representations?_x000a_This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata." id="25"/>
-    <tableColumn name="OC7: Justification" id="26"/>
-    <tableColumn name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? _x000a_This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features." id="27"/>
-    <tableColumn name="OC8: Justification" id="28"/>
-    <tableColumn name="OC9: Is the platform’s API documentation published in open access?_x000a_This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication." id="29"/>
-    <tableColumn name="OC9: Justification" id="30"/>
-    <tableColumn name="OC10: Is the platform’s API documentation clearly written and exemplified?_x000a_This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage." id="31"/>
-    <tableColumn name="OC10: Justification" id="32"/>
-    <tableColumn name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?_x000a_This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access." id="33"/>
-    <tableColumn name="OC11: Justification" id="34"/>
-    <tableColumn name="OC12: Does the platform’s API documentation detail the response format of each endpoint?_x000a_This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs." id="35"/>
-    <tableColumn name="OC12: Justification" id="36"/>
-    <tableColumn name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?_x000a_This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages." id="37"/>
-    <tableColumn name="OC13: Justification" id="38"/>
-    <tableColumn name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?_x000a_This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type." id="39"/>
-    <tableColumn name="OC14: Justification" id="40"/>
-    <tableColumn name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?_x000a_This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. " id="41"/>
-    <tableColumn name="OC15: Justification" id="42"/>
-    <tableColumn name="OC16: Can data from a publication’s comments be extracted using the platform’s API?_x000a_This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features." id="43"/>
-    <tableColumn name="OC16: Justification" id="44"/>
-    <tableColumn name="OC17: Can data from temporary content be extracted through the platform’s API?_x000a_This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features." id="45"/>
-    <tableColumn name="OC17: Justification" id="46"/>
-    <tableColumn name="OC18: Can historical data be extracted through the platform’s API?_x000a_This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved." id="47"/>
-    <tableColumn name="OC18: Justification" id="48"/>
-    <tableColumn name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?_x000a_This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously." id="49"/>
-    <tableColumn name="OC19: Justification" id="50"/>
-    <tableColumn name="OC20: Are the results returned by the API consistently reproducible?_x000a_This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly, including content that has been deleted between collections. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="51"/>
-    <tableColumn name="OC20: Justification" id="52"/>
-    <tableColumn name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?_x000a_This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="53"/>
-    <tableColumn name="OC21: Justification" id="54"/>
-    <tableColumn name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?_x000a_This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented." id="55"/>
-    <tableColumn name="OC22: Justification" id="56"/>
-    <tableColumn name="OC23: Does the platform’s API allow for filtering data based on publisher location?_x000a_This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location." id="57"/>
-    <tableColumn name="OC23: Justification" id="58"/>
-    <tableColumn name="OC24: Does the platform’s API allow for filtering data based on content language?_x000a_This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language." id="59"/>
-    <tableColumn name="OC24: Justification" id="60"/>
-    <tableColumn name="OC25: Does the platform’s API allow for filtering data by specific time periods?_x000a_This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges." id="61"/>
-    <tableColumn name="OC25: Justification" id="62"/>
-    <tableColumn name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?_x000a_This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data." id="63"/>
-    <tableColumn name="OC26: Justification" id="64"/>
+    <tableColumn id="1" name="Carimbo de data/hora"/>
+    <tableColumn id="2" name="Identification of analysts"/>
+    <tableColumn id="3" name="Which region is being analyzed?"/>
+    <tableColumn id="4" name="Which platform is being analyzed?"/>
+    <tableColumn id="5" name="SC1: Does the platform offer an API for collecting public user-generated content data?&#10;This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration."/>
+    <tableColumn id="6" name="SC1: Justification"/>
+    <tableColumn id="7" name="SC2: Can the full scope of public content data be extracted through the platform’s API?&#10;This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness."/>
+    <tableColumn id="8" name="SC2: Justification"/>
+    <tableColumn id="9" name="SC3: Is access to the platform’s API free of charge?&#10;This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access."/>
+    <tableColumn id="10" name="SC3: Justification"/>
+    <tableColumn id="11" name="SC4: Does the platform offer a graphical interface for extracting data?&#10;This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming."/>
+    <tableColumn id="12" name="SC4: Justification"/>
+    <tableColumn id="13" name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?&#10;This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms."/>
+    <tableColumn id="14" name="OC1: Justification"/>
+    <tableColumn id="15" name="OC2: Can the requested data be extracted directly from the platform’s API response?&#10;This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself."/>
+    <tableColumn id="16" name="OC2: Justification"/>
+    <tableColumn id="17" name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?&#10;This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access."/>
+    <tableColumn id="18" name="OC3: Justification"/>
+    <tableColumn id="19" name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?&#10;This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier."/>
+    <tableColumn id="20" name="OC4: Justification"/>
+    <tableColumn id="21" name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?&#10;This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author."/>
+    <tableColumn id="22" name="OC5: Justification"/>
+    <tableColumn id="23" name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?&#10;This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts."/>
+    <tableColumn id="24" name="OC6: Justification"/>
+    <tableColumn id="25" name="OC7: Does the API use locale-neutral data representations?&#10;This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata."/>
+    <tableColumn id="26" name="OC7: Justification"/>
+    <tableColumn id="27" name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? &#10;This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features."/>
+    <tableColumn id="28" name="OC8: Justification"/>
+    <tableColumn id="29" name="OC9: Is the platform’s API documentation published in open access?&#10;This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication."/>
+    <tableColumn id="30" name="OC9: Justification"/>
+    <tableColumn id="31" name="OC10: Is the platform’s API documentation clearly written and exemplified?&#10;This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage."/>
+    <tableColumn id="32" name="OC10: Justification"/>
+    <tableColumn id="33" name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?&#10;This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access."/>
+    <tableColumn id="34" name="OC11: Justification"/>
+    <tableColumn id="35" name="OC12: Does the platform’s API documentation detail the response format of each endpoint?&#10;This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs."/>
+    <tableColumn id="36" name="OC12: Justification"/>
+    <tableColumn id="37" name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?&#10;This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages."/>
+    <tableColumn id="38" name="OC13: Justification"/>
+    <tableColumn id="39" name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?&#10;This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type."/>
+    <tableColumn id="40" name="OC14: Justification"/>
+    <tableColumn id="41" name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?&#10;This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. "/>
+    <tableColumn id="42" name="OC15: Justification"/>
+    <tableColumn id="43" name="OC16: Can data from a publication’s comments be extracted using the platform’s API?&#10;This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features."/>
+    <tableColumn id="44" name="OC16: Justification"/>
+    <tableColumn id="45" name="OC17: Can data from temporary content be extracted through the platform’s API?&#10;This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features."/>
+    <tableColumn id="46" name="OC17: Justification"/>
+    <tableColumn id="47" name="OC18: Can historical data be extracted through the platform’s API?&#10;This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved."/>
+    <tableColumn id="48" name="OC18: Justification"/>
+    <tableColumn id="49" name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?&#10;This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously."/>
+    <tableColumn id="50" name="OC19: Justification"/>
+    <tableColumn id="51" name="OC20: Are the results returned by the API consistently reproducible?&#10;This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly, including content that has been deleted between collections. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
+    <tableColumn id="52" name="OC20: Justification"/>
+    <tableColumn id="53" name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?&#10;This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
+    <tableColumn id="54" name="OC21: Justification"/>
+    <tableColumn id="55" name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?&#10;This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented."/>
+    <tableColumn id="56" name="OC22: Justification"/>
+    <tableColumn id="57" name="OC23: Does the platform’s API allow for filtering data based on publisher location?&#10;This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location."/>
+    <tableColumn id="58" name="OC23: Justification"/>
+    <tableColumn id="59" name="OC24: Does the platform’s API allow for filtering data based on content language?&#10;This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language."/>
+    <tableColumn id="60" name="OC24: Justification"/>
+    <tableColumn id="61" name="OC25: Does the platform’s API allow for filtering data by specific time periods?&#10;This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges."/>
+    <tableColumn id="62" name="OC25: Justification"/>
+    <tableColumn id="63" name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?&#10;This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data."/>
+    <tableColumn id="64" name="OC26: Justification"/>
   </tableColumns>
-  <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4285F4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="EA4335"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="FBBC04"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="34A853"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="FF6D01"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="46BDC6"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="1155CC"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="1155CC"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:BR114"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" hidden="1" min="1" max="1" width="21.25"/>
-    <col customWidth="1" hidden="1" min="2" max="2" width="23.25"/>
-    <col customWidth="1" hidden="1" min="3" max="3" width="18.75"/>
-    <col customWidth="1" min="4" max="4" width="30.13"/>
-    <col customWidth="1" min="5" max="5" width="9.5"/>
-    <col customWidth="1" min="6" max="6" width="35.5"/>
-    <col customWidth="1" min="7" max="7" width="37.63"/>
-    <col customWidth="1" min="8" max="8" width="31.75"/>
-    <col customWidth="1" min="9" max="9" width="37.63"/>
-    <col customWidth="1" min="10" max="10" width="43.13"/>
-    <col customWidth="1" min="11" max="11" width="37.63"/>
-    <col customWidth="1" min="12" max="12" width="18.88"/>
-    <col customWidth="1" min="13" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="14" width="41.88"/>
-    <col customWidth="1" min="15" max="15" width="15.0"/>
-    <col customWidth="1" min="16" max="16" width="16.25"/>
-    <col customWidth="1" min="17" max="17" width="11.25"/>
-    <col customWidth="1" min="18" max="18" width="43.75"/>
-    <col customWidth="1" min="19" max="19" width="37.63"/>
-    <col customWidth="1" min="20" max="20" width="18.88"/>
-    <col customWidth="1" min="21" max="21" width="9.88"/>
-    <col customWidth="1" min="22" max="22" width="18.88"/>
-    <col customWidth="1" min="23" max="23" width="37.63"/>
-    <col customWidth="1" min="24" max="24" width="18.88"/>
-    <col customWidth="1" min="25" max="25" width="11.75"/>
-    <col customWidth="1" min="26" max="26" width="41.88"/>
-    <col customWidth="1" min="27" max="27" width="37.63"/>
-    <col customWidth="1" min="28" max="28" width="18.88"/>
-    <col customWidth="1" min="29" max="29" width="8.38"/>
-    <col customWidth="1" min="30" max="30" width="18.88"/>
-    <col customWidth="1" min="31" max="31" width="10.75"/>
-    <col customWidth="1" min="32" max="32" width="19.25"/>
-    <col customWidth="1" min="33" max="33" width="18.63"/>
-    <col customWidth="1" min="34" max="34" width="19.25"/>
-    <col customWidth="1" min="35" max="35" width="37.63"/>
-    <col customWidth="1" min="36" max="36" width="19.25"/>
-    <col customWidth="1" min="37" max="37" width="37.63"/>
-    <col customWidth="1" min="38" max="38" width="19.25"/>
-    <col customWidth="1" min="39" max="39" width="37.63"/>
-    <col customWidth="1" min="40" max="40" width="42.75"/>
-    <col customWidth="1" min="41" max="41" width="9.88"/>
-    <col customWidth="1" min="42" max="42" width="19.25"/>
-    <col customWidth="1" min="43" max="43" width="5.63"/>
-    <col customWidth="1" min="44" max="44" width="29.88"/>
-    <col customWidth="1" min="45" max="45" width="15.88"/>
-    <col customWidth="1" min="46" max="46" width="19.25"/>
-    <col customWidth="1" min="47" max="47" width="14.5"/>
-    <col customWidth="1" min="48" max="48" width="19.25"/>
-    <col customWidth="1" min="49" max="49" width="9.25"/>
-    <col customWidth="1" min="50" max="50" width="19.25"/>
-    <col customWidth="1" min="51" max="51" width="10.0"/>
-    <col customWidth="1" min="52" max="52" width="19.25"/>
-    <col customWidth="1" min="53" max="53" width="11.75"/>
-    <col customWidth="1" min="54" max="54" width="19.25"/>
-    <col customWidth="1" min="55" max="55" width="9.88"/>
-    <col customWidth="1" min="56" max="56" width="19.25"/>
-    <col customWidth="1" min="57" max="57" width="11.38"/>
-    <col customWidth="1" min="58" max="58" width="19.25"/>
-    <col customWidth="1" min="59" max="59" width="18.25"/>
-    <col customWidth="1" min="60" max="60" width="19.25"/>
-    <col customWidth="1" min="61" max="61" width="7.5"/>
-    <col customWidth="1" min="62" max="62" width="19.25"/>
-    <col customWidth="1" min="63" max="63" width="8.25"/>
-    <col customWidth="1" min="64" max="64" width="19.25"/>
-    <col customWidth="1" min="65" max="70" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="21.25"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="0" width="23.24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="0" width="18.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="43.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="41.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="43.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="41.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="8.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="42.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="5.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="9.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="0" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="7.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="65" style="0" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,25 +1210,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1497,55 +1240,55 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
@@ -1557,37 +1300,37 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
@@ -1599,49 +1342,49 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
       <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="1" t="s">
@@ -1654,9 +1397,9 @@
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
     </row>
-    <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
-        <v>45940.417001828704</v>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
+        <v>45940.4170018287</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>64</v>
@@ -1854,9 +1597,9 @@
       <c r="BQ2" s="7"/>
       <c r="BR2" s="7"/>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="4">
-        <v>45940.457484583334</v>
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
+        <v>45940.4574845833</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>71</v>
@@ -2054,9 +1797,9 @@
       <c r="BQ3" s="7"/>
       <c r="BR3" s="7"/>
     </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="4">
-        <v>45940.457484583334</v>
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>45940.4574845833</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>71</v>
@@ -2071,7 +1814,7 @@
         <v>66</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>66</v>
@@ -2254,198 +1997,198 @@
       <c r="BQ4" s="7"/>
       <c r="BR4" s="7"/>
     </row>
-    <row r="5" ht="159.0" customHeight="1">
-      <c r="A5" s="4">
-        <v>45954.67528591435</v>
+    <row r="5" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>45954.6752859144</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="Q5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="U5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="W5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="W5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="X5" s="5" t="s">
+      <c r="Y5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z5" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="AA5" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="AC5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD5" s="5" t="s">
+      <c r="AE5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="AE5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF5" s="5" t="s">
+      <c r="AG5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH5" s="8" t="s">
+      <c r="AI5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="AI5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
+      <c r="AK5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL5" s="5" t="s">
+      <c r="AM5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="AM5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN5" s="5" t="s">
+      <c r="AO5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP5" s="5" t="s">
+      <c r="AQ5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AQ5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR5" s="9" t="s">
+      <c r="AS5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AS5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT5" s="5" t="s">
+      <c r="AU5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AU5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV5" s="5" t="s">
+      <c r="AW5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AW5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX5" s="5" t="s">
+      <c r="AY5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AY5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ5" s="5" t="s">
+      <c r="BA5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="BA5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB5" s="5" t="s">
+      <c r="BC5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="BC5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD5" s="5" t="s">
+      <c r="BE5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="BE5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF5" s="5" t="s">
+      <c r="BG5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="BG5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH5" s="5" t="s">
+      <c r="BI5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="BI5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ5" s="5" t="s">
+      <c r="BK5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL5" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="BK5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL5" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="BM5" s="7"/>
       <c r="BN5" s="7"/>
@@ -2454,198 +2197,198 @@
       <c r="BQ5" s="7"/>
       <c r="BR5" s="7"/>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="4">
-        <v>45957.42411390046</v>
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>45957.4241139005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="O6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AQ6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AS6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AU6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AW6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AY6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BM6" s="7"/>
       <c r="BN6" s="7"/>
@@ -2654,198 +2397,198 @@
       <c r="BQ6" s="7"/>
       <c r="BR6" s="7"/>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="4">
-        <v>45957.428492453706</v>
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>45957.4284924537</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="O7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AA7" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AM7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AO7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AQ7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AS7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AU7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AW7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AY7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BM7" s="7"/>
       <c r="BN7" s="7"/>
@@ -2854,198 +2597,198 @@
       <c r="BQ7" s="7"/>
       <c r="BR7" s="7"/>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="4">
-        <v>45957.43270828704</v>
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>45957.432708287</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="O8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="W8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA8" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AO8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AQ8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AS8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AU8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AW8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AY8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BA8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BM8" s="7"/>
       <c r="BN8" s="7"/>
@@ -3054,198 +2797,198 @@
       <c r="BQ8" s="7"/>
       <c r="BR8" s="7"/>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="10">
-        <v>45960.65751310185</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>45960.6575131019</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="O9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA9" s="9" t="s">
+      <c r="Q9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AI9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AM9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AQ9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AS9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AU9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AW9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AY9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BA9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BC9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL9" s="9" t="s">
-        <v>139</v>
+      <c r="AB9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AQ9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AS9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AW9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BA9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL9" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="BM9" s="7"/>
       <c r="BN9" s="7"/>
@@ -3254,198 +2997,198 @@
       <c r="BQ9" s="7"/>
       <c r="BR9" s="7"/>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="10">
-        <v>45961.43548726852</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>45961.4354872685</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="M10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA10" s="9" t="s">
+      <c r="O10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AQ10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AS10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AY10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BC10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BG10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BI10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BK10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL10" s="9" t="s">
-        <v>143</v>
+      <c r="AB10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AW10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AY10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BE10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BI10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BK10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL10" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="BM10" s="7"/>
       <c r="BN10" s="7"/>
@@ -3454,198 +3197,198 @@
       <c r="BQ10" s="7"/>
       <c r="BR10" s="7"/>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="10">
-        <v>45961.685883865735</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>45961.6858838657</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA11" s="9" t="s">
+      <c r="M11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AG11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AS11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AW11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BA11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BC11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BG11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BI11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BK11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL11" s="9" t="s">
-        <v>149</v>
+      <c r="AB11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AS11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AW11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BG11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL11" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="BM11" s="7"/>
       <c r="BN11" s="7"/>
@@ -3654,198 +3397,198 @@
       <c r="BQ11" s="7"/>
       <c r="BR11" s="7"/>
     </row>
-    <row r="12" ht="249.75" customHeight="1">
-      <c r="A12" s="10">
-        <v>45966.82094762732</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>45966.8209476273</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="9" t="s">
+      <c r="O12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="AC12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF12" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH12" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP12" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR12" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AS12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z12" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB12" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD12" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="AG12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH12" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="AI12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL12" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN12" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="AO12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="AQ12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR12" s="9" t="s">
+      <c r="AT12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AS12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT12" s="9" t="s">
+      <c r="AU12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV12" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="AU12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV12" s="9" t="s">
+      <c r="AW12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX12" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="AW12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX12" s="9" t="s">
+      <c r="AY12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ12" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="AY12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ12" s="9" t="s">
+      <c r="BA12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB12" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="BA12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB12" s="9" t="s">
+      <c r="BC12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="BC12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD12" s="9" t="s">
+      <c r="BE12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF12" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="BE12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF12" s="9" t="s">
+      <c r="BG12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH12" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="BG12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH12" s="9" t="s">
+      <c r="BI12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ12" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="BI12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ12" s="9" t="s">
+      <c r="BK12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL12" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="BK12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL12" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
@@ -3854,198 +3597,198 @@
       <c r="BQ12" s="7"/>
       <c r="BR12" s="7"/>
     </row>
-    <row r="13" ht="151.5" customHeight="1">
-      <c r="A13" s="10">
-        <v>45968.52448232639</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="9" t="s">
+    <row r="13" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>45968.5244823264</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="9" t="s">
+      <c r="O13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="AM13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD13" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF13" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH13" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ13" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL13" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN13" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="AO13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP13" s="9" t="s">
+      <c r="AR13" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="AQ13" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR13" s="9" t="s">
+      <c r="AS13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT13" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="AS13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT13" s="9" t="s">
+      <c r="AU13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV13" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="AU13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV13" s="9" t="s">
+      <c r="AW13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX13" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="AW13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX13" s="9" t="s">
+      <c r="AY13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ13" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="AY13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ13" s="9" t="s">
+      <c r="BA13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB13" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="BA13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB13" s="9" t="s">
+      <c r="BC13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="BC13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD13" s="9" t="s">
+      <c r="BE13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF13" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="BE13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF13" s="9" t="s">
+      <c r="BG13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH13" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="BG13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH13" s="9" t="s">
+      <c r="BI13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ13" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="BI13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ13" s="9" t="s">
+      <c r="BK13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL13" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="BK13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL13" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="BM13" s="7"/>
       <c r="BN13" s="7"/>
@@ -4054,198 +3797,198 @@
       <c r="BQ13" s="7"/>
       <c r="BR13" s="7"/>
     </row>
-    <row r="14" ht="250.5" customHeight="1">
-      <c r="A14" s="10">
-        <v>45971.72617731482</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" s="9" t="s">
+    <row r="14" customFormat="false" ht="250.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>45971.7261773148</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="9" t="s">
+      <c r="I14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R14" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="O14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R14" s="9" t="s">
+      <c r="S14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="S14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="U14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V14" s="9" t="s">
+      <c r="W14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="W14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X14" s="9" t="s">
+      <c r="Y14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z14" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="Y14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z14" s="9" t="s">
+      <c r="AA14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB14" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="AA14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB14" s="9" t="s">
+      <c r="AC14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD14" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AC14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD14" s="9" t="s">
+      <c r="AE14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF14" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AE14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF14" s="9" t="s">
+      <c r="AG14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH14" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="AG14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH14" s="9" t="s">
+      <c r="AI14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="AI14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ14" s="9" t="s">
+      <c r="AK14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL14" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="AK14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL14" s="9" t="s">
+      <c r="AM14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN14" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="AM14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN14" s="9" t="s">
+      <c r="AO14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP14" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="AO14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP14" s="9" t="s">
+      <c r="AQ14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR14" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="AQ14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR14" s="9" t="s">
+      <c r="AS14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT14" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="AS14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT14" s="9" t="s">
+      <c r="AU14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV14" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="AU14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV14" s="9" t="s">
+      <c r="AW14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX14" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AW14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX14" s="9" t="s">
+      <c r="AY14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ14" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="AY14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ14" s="9" t="s">
+      <c r="BA14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB14" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="BA14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB14" s="9" t="s">
+      <c r="BC14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD14" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="BC14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD14" s="9" t="s">
+      <c r="BE14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF14" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="BE14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF14" s="9" t="s">
+      <c r="BG14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH14" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="BG14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH14" s="9" t="s">
+      <c r="BI14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ14" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="BI14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ14" s="9" t="s">
+      <c r="BK14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL14" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="BK14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL14" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="BM14" s="7"/>
       <c r="BN14" s="7"/>
@@ -4254,7 +3997,7 @@
       <c r="BQ14" s="7"/>
       <c r="BR14" s="7"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4326,7 +4069,7 @@
       <c r="BQ15" s="7"/>
       <c r="BR15" s="7"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -4398,7 +4141,7 @@
       <c r="BQ16" s="7"/>
       <c r="BR16" s="7"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -4470,7 +4213,7 @@
       <c r="BQ17" s="7"/>
       <c r="BR17" s="7"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -4542,7 +4285,7 @@
       <c r="BQ18" s="7"/>
       <c r="BR18" s="7"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4614,7 +4357,7 @@
       <c r="BQ19" s="7"/>
       <c r="BR19" s="7"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -4686,7 +4429,7 @@
       <c r="BQ20" s="7"/>
       <c r="BR20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -4758,7 +4501,7 @@
       <c r="BQ21" s="7"/>
       <c r="BR21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -4830,7 +4573,7 @@
       <c r="BQ22" s="7"/>
       <c r="BR22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -4902,7 +4645,7 @@
       <c r="BQ23" s="7"/>
       <c r="BR23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -4974,7 +4717,7 @@
       <c r="BQ24" s="7"/>
       <c r="BR24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -5046,7 +4789,7 @@
       <c r="BQ25" s="7"/>
       <c r="BR25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -5118,7 +4861,7 @@
       <c r="BQ26" s="7"/>
       <c r="BR26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -5190,7 +4933,7 @@
       <c r="BQ27" s="7"/>
       <c r="BR27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -5262,7 +5005,7 @@
       <c r="BQ28" s="7"/>
       <c r="BR28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -5334,7 +5077,7 @@
       <c r="BQ29" s="7"/>
       <c r="BR29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -5406,7 +5149,7 @@
       <c r="BQ30" s="7"/>
       <c r="BR30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -5478,7 +5221,7 @@
       <c r="BQ31" s="7"/>
       <c r="BR31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -5550,7 +5293,7 @@
       <c r="BQ32" s="7"/>
       <c r="BR32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -5622,7 +5365,7 @@
       <c r="BQ33" s="7"/>
       <c r="BR33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -5694,7 +5437,7 @@
       <c r="BQ34" s="7"/>
       <c r="BR34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -5766,7 +5509,7 @@
       <c r="BQ35" s="7"/>
       <c r="BR35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -5838,7 +5581,7 @@
       <c r="BQ36" s="7"/>
       <c r="BR36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -5910,7 +5653,7 @@
       <c r="BQ37" s="7"/>
       <c r="BR37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -5982,7 +5725,7 @@
       <c r="BQ38" s="7"/>
       <c r="BR38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -6054,7 +5797,7 @@
       <c r="BQ39" s="7"/>
       <c r="BR39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -6126,7 +5869,7 @@
       <c r="BQ40" s="7"/>
       <c r="BR40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -6198,7 +5941,7 @@
       <c r="BQ41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -6270,7 +6013,7 @@
       <c r="BQ42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -6342,7 +6085,7 @@
       <c r="BQ43" s="7"/>
       <c r="BR43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6414,7 +6157,7 @@
       <c r="BQ44" s="7"/>
       <c r="BR44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -6486,7 +6229,7 @@
       <c r="BQ45" s="7"/>
       <c r="BR45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -6558,7 +6301,7 @@
       <c r="BQ46" s="7"/>
       <c r="BR46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -6630,7 +6373,7 @@
       <c r="BQ47" s="7"/>
       <c r="BR47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -6702,7 +6445,7 @@
       <c r="BQ48" s="7"/>
       <c r="BR48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6774,7 +6517,7 @@
       <c r="BQ49" s="7"/>
       <c r="BR49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -6846,7 +6589,7 @@
       <c r="BQ50" s="7"/>
       <c r="BR50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -6918,7 +6661,7 @@
       <c r="BQ51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -6990,7 +6733,7 @@
       <c r="BQ52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -7062,7 +6805,7 @@
       <c r="BQ53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -7134,7 +6877,7 @@
       <c r="BQ54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -7206,7 +6949,7 @@
       <c r="BQ55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -7278,7 +7021,7 @@
       <c r="BQ56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -7350,7 +7093,7 @@
       <c r="BQ57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -7422,7 +7165,7 @@
       <c r="BQ58" s="7"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -7494,7 +7237,7 @@
       <c r="BQ59" s="7"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -7566,7 +7309,7 @@
       <c r="BQ60" s="7"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -7638,7 +7381,7 @@
       <c r="BQ61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -7710,7 +7453,7 @@
       <c r="BQ62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -7782,7 +7525,7 @@
       <c r="BQ63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -7854,7 +7597,7 @@
       <c r="BQ64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -7926,7 +7669,7 @@
       <c r="BQ65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -7998,7 +7741,7 @@
       <c r="BQ66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -8070,7 +7813,7 @@
       <c r="BQ67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -8142,7 +7885,7 @@
       <c r="BQ68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -8214,7 +7957,7 @@
       <c r="BQ69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -8286,7 +8029,7 @@
       <c r="BQ70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -8358,7 +8101,7 @@
       <c r="BQ71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -8430,7 +8173,7 @@
       <c r="BQ72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -8502,7 +8245,7 @@
       <c r="BQ73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -8574,7 +8317,7 @@
       <c r="BQ74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -8646,7 +8389,7 @@
       <c r="BQ75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -8718,7 +8461,7 @@
       <c r="BQ76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -8790,7 +8533,7 @@
       <c r="BQ77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -8862,7 +8605,7 @@
       <c r="BQ78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -8934,7 +8677,7 @@
       <c r="BQ79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -9006,7 +8749,7 @@
       <c r="BQ80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -9078,7 +8821,7 @@
       <c r="BQ81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -9150,7 +8893,7 @@
       <c r="BQ82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -9222,7 +8965,7 @@
       <c r="BQ83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -9294,7 +9037,7 @@
       <c r="BQ84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -9366,7 +9109,7 @@
       <c r="BQ85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9438,7 +9181,7 @@
       <c r="BQ86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -9510,7 +9253,7 @@
       <c r="BQ87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -9582,7 +9325,7 @@
       <c r="BQ88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -9654,7 +9397,7 @@
       <c r="BQ89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -9726,7 +9469,7 @@
       <c r="BQ90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -9798,7 +9541,7 @@
       <c r="BQ91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -9870,7 +9613,7 @@
       <c r="BQ92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -9942,7 +9685,7 @@
       <c r="BQ93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -10014,7 +9757,7 @@
       <c r="BQ94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -10086,7 +9829,7 @@
       <c r="BQ95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -10158,7 +9901,7 @@
       <c r="BQ96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -10230,7 +9973,7 @@
       <c r="BQ97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -10302,7 +10045,7 @@
       <c r="BQ98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -10374,7 +10117,7 @@
       <c r="BQ99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -10446,7 +10189,7 @@
       <c r="BQ100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -10518,7 +10261,7 @@
       <c r="BQ101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -10590,7 +10333,7 @@
       <c r="BQ102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -10662,7 +10405,7 @@
       <c r="BQ103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -10734,7 +10477,7 @@
       <c r="BQ104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -10806,7 +10549,7 @@
       <c r="BQ105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -10878,7 +10621,7 @@
       <c r="BQ106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -10950,7 +10693,7 @@
       <c r="BQ107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -11022,7 +10765,7 @@
       <c r="BQ108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -11094,7 +10837,7 @@
       <c r="BQ109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -11166,7 +10909,7 @@
       <c r="BQ110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -11238,7 +10981,7 @@
       <c r="BQ111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -11310,7 +11053,7 @@
       <c r="BQ112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -11382,7 +11125,7 @@
       <c r="BQ113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -11456,16 +11199,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F3"/>
-    <hyperlink r:id="rId2" ref="F4"/>
-    <hyperlink r:id="rId3" ref="N5"/>
-    <hyperlink r:id="rId4" ref="AH5"/>
-    <hyperlink r:id="rId5" ref="F11"/>
-    <hyperlink r:id="rId6" ref="AH12"/>
+    <hyperlink ref="F3" r:id="rId1" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
+    <hyperlink ref="F4" r:id="rId2" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
+    <hyperlink ref="N5" r:id="rId3" display="This question is not applicable for Bluesky, because:&#10;* There is no specific authentication for researchers.&#10;* There is no private accounts or posts at Bluesky&#10;* There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.&#10;Source: &#10;&#10;https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb &#10;&#10;https://atproto.blue/en/latest/dm.html"/>
+    <hyperlink ref="AH5" r:id="rId4" display="Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only &quot;recomendations&quot; to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines"/>
+    <hyperlink ref="F11" r:id="rId5" display="Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for &quot;pins&quot; of the &quot;operation user_account&quot;. The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags"/>
+    <hyperlink ref="AH12" r:id="rId6" display="The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.&#10;https://developers.google.com/youtube/v3/docs &#10;https://developers.google.com/youtube/terms"/>
   </hyperlinks>
-  <drawing r:id="rId7"/>
-  <tableParts count="1">
-    <tablePart r:id="rId9"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
+++ b/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
@@ -1,340 +1,375 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Respostas ao formulário 1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$BL$14</definedName>
+  </definedNames>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="238">
-  <si>
-    <t xml:space="preserve">Carimbo de data/hora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identification of analysts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which region is being analyzed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which platform is being analyzed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC1: Does the platform offer an API for collecting public user-generated content data?
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="239">
+  <si>
+    <t>Carimbo de data/hora</t>
+  </si>
+  <si>
+    <t>Identification of analysts</t>
+  </si>
+  <si>
+    <t>Which region is being analyzed?</t>
+  </si>
+  <si>
+    <t>Which platform is being analyzed?</t>
+  </si>
+  <si>
+    <t>SC1: Does the platform offer an API for collecting public user-generated content data?
 This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration.</t>
   </si>
   <si>
-    <t xml:space="preserve">SC1: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC2: Can the full scope of public content data be extracted through the platform’s API?
+    <t>SC1: Justification</t>
+  </si>
+  <si>
+    <t>SC2: Can the full scope of public content data be extracted through the platform’s API?
 This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness.</t>
   </si>
   <si>
-    <t xml:space="preserve">SC2: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC3: Is access to the platform’s API free of charge?
+    <t>SC2: Justification</t>
+  </si>
+  <si>
+    <t>SC3: Is access to the platform’s API free of charge?
 This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access.</t>
   </si>
   <si>
-    <t xml:space="preserve">SC3: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC4: Does the platform offer a graphical interface for extracting data?
+    <t>SC3: Justification</t>
+  </si>
+  <si>
+    <t>SC4: Does the platform offer a graphical interface for extracting data?
 This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming.</t>
   </si>
   <si>
-    <t xml:space="preserve">SC4: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
+    <t>SC4: Justification</t>
+  </si>
+  <si>
+    <t>OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
 This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC1: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC2: Can the requested data be extracted directly from the platform’s API response?
+    <t>OC1: Justification</t>
+  </si>
+  <si>
+    <t>OC2: Can the requested data be extracted directly from the platform’s API response?
 This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC2: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
+    <t>OC2: Justification</t>
+  </si>
+  <si>
+    <t>OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
 This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC3: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
+    <t>OC3: Justification</t>
+  </si>
+  <si>
+    <t>OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
 This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC4: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
+    <t>OC4: Justification</t>
+  </si>
+  <si>
+    <t>OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
 This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC5: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
+    <t>OC5: Justification</t>
+  </si>
+  <si>
+    <t>OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
 This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC6: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC7: Does the API use locale-neutral data representations?
+    <t>OC6: Justification</t>
+  </si>
+  <si>
+    <t>OC7: Does the API use locale-neutral data representations?
 This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC7: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
+    <t>OC7: Justification</t>
+  </si>
+  <si>
+    <t>OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
 This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC8: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC9: Is the platform’s API documentation published in open access?
+    <t>OC8: Justification</t>
+  </si>
+  <si>
+    <t>OC9: Is the platform’s API documentation published in open access?
 This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC9: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC10: Is the platform’s API documentation clearly written and exemplified?
+    <t>OC9: Justification</t>
+  </si>
+  <si>
+    <t>OC10: Is the platform’s API documentation clearly written and exemplified?
 This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC10: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
+    <t>OC10: Justification</t>
+  </si>
+  <si>
+    <t>OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
 This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC11: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC12: Does the platform’s API documentation detail the response format of each endpoint?
+    <t>OC11: Justification</t>
+  </si>
+  <si>
+    <t>OC12: Does the platform’s API documentation detail the response format of each endpoint?
 This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC12: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC13: Does the platform provide its API documentation in the official languages of the assessed region?
+    <t>OC12: Justification</t>
+  </si>
+  <si>
+    <t>OC13: Does the platform provide its API documentation in the official languages of the assessed region?
 This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC13: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
+    <t>OC13: Justification</t>
+  </si>
+  <si>
+    <t>OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
 This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC14: Justification</t>
+    <t>OC14: Justification</t>
   </si>
   <si>
     <t xml:space="preserve">OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?
 This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. </t>
   </si>
   <si>
-    <t xml:space="preserve">OC15: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC16: Can data from a publication’s comments be extracted using the platform’s API?
+    <t>OC15: Justification</t>
+  </si>
+  <si>
+    <t>OC16: Can data from a publication’s comments be extracted using the platform’s API?
 This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC16: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC17: Can data from temporary content be extracted through the platform’s API?
+    <t>OC16: Justification</t>
+  </si>
+  <si>
+    <t>OC17: Can data from temporary content be extracted through the platform’s API?
 This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC17: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC18: Can historical data be extracted through the platform’s API?
+    <t>OC17: Justification</t>
+  </si>
+  <si>
+    <t>OC18: Can historical data be extracted through the platform’s API?
 This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC18: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
+    <t>OC18: Justification</t>
+  </si>
+  <si>
+    <t>OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
 This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC19: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC20: Are the results returned by the API consistently reproducible?
-This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly, including content that has been deleted between collections. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC20: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
+    <t>OC19: Justification</t>
+  </si>
+  <si>
+    <t>OC20: Are the results returned by the API consistently reproducible?
+This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
+  </si>
+  <si>
+    <t>OC20: Justification</t>
+  </si>
+  <si>
+    <t>OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
 This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC21: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
+    <t>OC21: Justification</t>
+  </si>
+  <si>
+    <t>OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
 This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC22: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC23: Does the platform’s API allow for filtering data based on publisher location?
+    <t>OC22: Justification</t>
+  </si>
+  <si>
+    <t>OC23: Does the platform’s API allow for filtering data based on publisher location?
 This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC23: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC24: Does the platform’s API allow for filtering data based on content language?
+    <t>OC23: Justification</t>
+  </si>
+  <si>
+    <t>OC24: Does the platform’s API allow for filtering data based on content language?
 This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC24: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC25: Does the platform’s API allow for filtering data by specific time periods?
+    <t>OC24: Justification</t>
+  </si>
+  <si>
+    <t>OC25: Does the platform’s API allow for filtering data by specific time periods?
 This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC25: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OC26: Can data from newly published content be extracted from the platform’s API in near real time?
+    <t>OC25: Justification</t>
+  </si>
+  <si>
+    <t>OC26: Can data from newly published content be extracted from the platform’s API in near real time?
 This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data.</t>
   </si>
   <si>
-    <t xml:space="preserve">OC26: Justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Gabriel Haddad and Vinicius Branco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No or not applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Mello and João Gabriel Haddad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instagram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
+    <t>OC26: Justification</t>
+  </si>
+  <si>
+    <t>João Gabriel Haddad and Vinicius Branco</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t>(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t>(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t>No or not applicable</t>
+  </si>
+  <si>
+    <t>Danielle Mello and João Gabriel Haddad</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
+https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
+    </r>
+  </si>
+  <si>
+    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
+    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
+    <t>Yes, but only for approved researchers</t>
+  </si>
+  <si>
+    <t>Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
-https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, but only for approved researchers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Haddad e Vinicius Scortegagna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bluesky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
+    </r>
+  </si>
+  <si>
+    <t>João Haddad e Vinicius Scortegagna</t>
+  </si>
+  <si>
+    <t>Bluesky</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
   </si>
   <si>
     <t xml:space="preserve">All public content data can be extracted through the API. </t>
   </si>
   <si>
-    <t xml:space="preserve">The platforms requires only a BlueSky account to access the API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not applicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This question is not applicable for Bluesky, because:
+    <t>The platforms requires only a BlueSky account to access the API</t>
+  </si>
+  <si>
+    <t>The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">This question is not applicable for Bluesky, because:
 * There is no specific authentication for researchers.
 * There is no private accounts or posts at Bluesky
 * There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.
 Source: 
 https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb 
-https://atproto.blue/en/latest/dm.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF434343"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://atproto.blue/en/latest/dm.html</t>
+    </r>
+  </si>
+  <si>
+    <t>Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
+  </si>
+  <si>
+    <t>Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an endpoint for extrating data from an individual publication. </t>
@@ -350,41 +385,51 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">We did not find a change log in official API documentation, only reference for a change log from a developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Bluesky API only provides a way to a post author self-label the post content. 
+    <t>We did not find a change log in official API documentation, only reference for a change log from a developer</t>
+  </si>
+  <si>
+    <t>It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
+  </si>
+  <si>
+    <t>The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint. In its website, Bluesky makes reference to another documentation, related to its Python SDK. This documentation is clearly written and exemplified, however, we do not considered in our analisys because it was made by an independent developer</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://docs.bsky.app/docs/support/developer-guidelines</t>
+    </r>
+  </si>
+  <si>
+    <t>Although some endpoints lack explanation, there is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
+  </si>
+  <si>
+    <t>The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t>The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t>The Bluesky API only provides a way to a post author self-label the post content. 
 * Check [SelfLabel definition](https://atproto.blue/en/latest/atproto/atproto_client.models.com.atproto.label.defs.html#atproto_client.models.com.atproto.label.defs.SelfLabel). However, there is no specific label for AI-generated content.</t>
   </si>
   <si>
-    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bluesky does not have temporary content features.</t>
+    <t>Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t>Bluesky does not have temporary content features.</t>
   </si>
   <si>
     <t xml:space="preserve">It is possible to extract historical data through the API. </t>
   </si>
   <si>
-    <t xml:space="preserve">During our tests, we were able to obtain almost 10,000 (over 9,900) publications in only five minutes. </t>
+    <t xml:space="preserve">During our tests, we were able to obtain more than 10,000 publications in less than 10 minutes. </t>
   </si>
   <si>
     <t xml:space="preserve">The same request was made five times imediately after another and the same results were retrieved. </t>
@@ -408,125 +453,139 @@
     <t xml:space="preserve">Data can be extrated in near real time in Bluesky. </t>
   </si>
   <si>
-    <t xml:space="preserve">Fernando Ferreira &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Tadeu &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle and Adriano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapchat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
+    <t>Fernando Ferreira &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t>WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
+  </si>
+  <si>
+    <t>TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
+  </si>
+  <si>
+    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t>TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
+  </si>
+  <si>
+    <t>Rafael Tadeu &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t>Kwai</t>
+  </si>
+  <si>
+    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t>Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t>Danielle and Adriano</t>
+  </si>
+  <si>
+    <t>Snapchat</t>
+  </si>
+  <si>
+    <t>Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
 Source: https://developers.snap.com/api/home https://developers.snap.com/api/marketing-api/Public-Profile-API/GetStarted https://developers.snap.com/api/marketing-api/Public-Profile-API/CreatorDiscovery</t>
   </si>
   <si>
-    <t xml:space="preserve">Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t>Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t xml:space="preserve">The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t>The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t xml:space="preserve">Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
+    <t>Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
+  </si>
+  <si>
+    <t>The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t xml:space="preserve">Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felipe Grael &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Gabriel Haddad &amp; Vinícius Branco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinterest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriano Belisario e Lucas Murakami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
+    <t>Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
+  </si>
+  <si>
+    <t>Felipe Grael &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t>Discord</t>
+  </si>
+  <si>
+    <t>The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
+  </si>
+  <si>
+    <t>Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t>Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t>João Gabriel Haddad &amp; Vinícius Branco</t>
+  </si>
+  <si>
+    <t>Pinterest</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve"> and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
+    </r>
+  </si>
+  <si>
+    <t>Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
+  </si>
+  <si>
+    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t>Adriano Belisario e Lucas Murakami</t>
+  </si>
+  <si>
+    <t>YouTube</t>
+  </si>
+  <si>
+    <t>The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
 https://developers.google.com/youtube/v3/docs.</t>
   </si>
   <si>
@@ -585,9 +644,19 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
+    <r>
+      <rPr/>
+      <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
 https://developers.google.com/youtube/v3/docs 
-https://developers.google.com/youtube/terms</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://developers.google.com/youtube/terms</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Each method in the YouTube Data API v3 includes an example of its response format.
@@ -631,11 +700,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The documentation does not guarantee that API results are consistently reproducible and explicitly acknowledges approximations in key metrics. We made the same request to the search list endpoint multiple times, using “relevance” for the order parameter. The results differed in the order of the returned items. Additionally, after deletion, YouTube videos and comments cannot be queried. 
-</t>
+    <t>The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
+  </si>
+  <si>
+    <t>The documentation does not guarantee that API results are consistently reproducible and explicitly acknowledges approximations in key metrics. We made the same request to the search list endpoint multiple times, using “relevance” for the order parameter. The results differed in the order of the returned items.</t>
   </si>
   <si>
     <t xml:space="preserve">There are frequent inconsistencies, even in collections using fixed parameters. In our tests, we found that the YouTube API does not necessarily honor user-defined filters. For instance, the documentation about the “relevanceLanguage” filter states that “results in other languages will still be returned if they are highly relevant to the search query term”, meaning the language filter operates as a soft preference rather than a strict constraint, allowing inconsistent results. In our tests, we confirmed that when requesting videos in Portuguese, one of the resulting items used English for its description and title. Also, comments were written in English. Although the video had no spoken dialogue —only images and English text —the previous statements already indicate that the video is targeted for English-speaking audiences. Recent academic studies have also addressed these consistency issues.
@@ -645,7 +713,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
+    <t>We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
   </si>
   <si>
     <t xml:space="preserve">The API does not support filtering by channel/publisher location. This feature was deprecated from API v2. Currently, the “search.list” endpoint includes a location parameter, but this applies to video geographic metadata (where content was filmed), not channel/publisher location. The “regionCode” parameter "instructs the API to return search results for videos that can be viewed in the specified country", filtering by content availability region, not by publishers’ location.
@@ -668,94 +736,94 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The API documentation is available only in English (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The platform returns data which matches the parameters and filters applied.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telegram</t>
+    <t>X</t>
+  </si>
+  <si>
+    <t>X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
+  </si>
+  <si>
+    <t>Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
+  </si>
+  <si>
+    <t>In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
+  </si>
+  <si>
+    <t>X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
+  </si>
+  <si>
+    <t>If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
+  </si>
+  <si>
+    <t>The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
+  </si>
+  <si>
+    <t>The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
+  </si>
+  <si>
+    <t>The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
+  </si>
+  <si>
+    <t>Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
+  </si>
+  <si>
+    <t>The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
+  </si>
+  <si>
+    <t>The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t>The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
+  </si>
+  <si>
+    <t>The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
+  </si>
+  <si>
+    <t>For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
+  </si>
+  <si>
+    <t>The API documentation is available only in English (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t>The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t>X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
+  </si>
+  <si>
+    <t>Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t>The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
+  </si>
+  <si>
+    <t>Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
+  </si>
+  <si>
+    <t>Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t>Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
+  </si>
+  <si>
+    <t>The platform returns data which matches the parameters and filters applied.</t>
+  </si>
+  <si>
+    <t>The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
+  </si>
+  <si>
+    <t>The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
+  </si>
+  <si>
+    <t>The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
+  </si>
+  <si>
+    <t>The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
+  </si>
+  <si>
+    <t>In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
+  </si>
+  <si>
+    <t>Telegram</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an API that allows the collection of public data in Telegram conversations.
@@ -769,10 +837,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">All Telegram APIs are free of charge: https://core.telegram.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
+    <t>All Telegram APIs are free of charge: https://core.telegram.org/</t>
+  </si>
+  <si>
+    <t>Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram API access requires an access key that remains the same even after logging in multiple times. It will only change in specific situations, and the API provides the necessary methods to update it programmatically.
@@ -808,7 +876,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
+    <t>Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
   </si>
   <si>
     <t xml:space="preserve">The Telegram and TDLib API documentation is not clearly written or exemplified. While it provides a technical reference of available classes and methods, it lacks detailed explanations and practical examples demonstrating how to call endpoints or implement typical workflows. The documentation’s structure assumes prior familiarity with Telegram’s internal architecture, making it difficult for developers to understand usage without relying on third-party resources or community libraries.
@@ -836,7 +904,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
+    <t>We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram allows extracting comments from channels with discussion features enabled. Each comment is treated as a reply within a message thread, which can be retrieved as structured data.
@@ -870,7 +938,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
+    <t>Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram’s TDLib and core API do not include any parameters or methods that enable filtering data based on the language of message content.
@@ -892,48 +960,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="11"/>
+      <u/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -941,263 +992,474 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="14">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF3D3D3D"/>
+          <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
+      <border/>
     </dxf>
     <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="Respostas ao formulário 1-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BL14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BL14" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$BL$14"/>
   <tableColumns count="64">
-    <tableColumn id="1" name="Carimbo de data/hora"/>
-    <tableColumn id="2" name="Identification of analysts"/>
-    <tableColumn id="3" name="Which region is being analyzed?"/>
-    <tableColumn id="4" name="Which platform is being analyzed?"/>
-    <tableColumn id="5" name="SC1: Does the platform offer an API for collecting public user-generated content data?&#10;This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration."/>
-    <tableColumn id="6" name="SC1: Justification"/>
-    <tableColumn id="7" name="SC2: Can the full scope of public content data be extracted through the platform’s API?&#10;This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness."/>
-    <tableColumn id="8" name="SC2: Justification"/>
-    <tableColumn id="9" name="SC3: Is access to the platform’s API free of charge?&#10;This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access."/>
-    <tableColumn id="10" name="SC3: Justification"/>
-    <tableColumn id="11" name="SC4: Does the platform offer a graphical interface for extracting data?&#10;This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming."/>
-    <tableColumn id="12" name="SC4: Justification"/>
-    <tableColumn id="13" name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?&#10;This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms."/>
-    <tableColumn id="14" name="OC1: Justification"/>
-    <tableColumn id="15" name="OC2: Can the requested data be extracted directly from the platform’s API response?&#10;This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself."/>
-    <tableColumn id="16" name="OC2: Justification"/>
-    <tableColumn id="17" name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?&#10;This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access."/>
-    <tableColumn id="18" name="OC3: Justification"/>
-    <tableColumn id="19" name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?&#10;This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier."/>
-    <tableColumn id="20" name="OC4: Justification"/>
-    <tableColumn id="21" name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?&#10;This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author."/>
-    <tableColumn id="22" name="OC5: Justification"/>
-    <tableColumn id="23" name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?&#10;This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts."/>
-    <tableColumn id="24" name="OC6: Justification"/>
-    <tableColumn id="25" name="OC7: Does the API use locale-neutral data representations?&#10;This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata."/>
-    <tableColumn id="26" name="OC7: Justification"/>
-    <tableColumn id="27" name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? &#10;This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features."/>
-    <tableColumn id="28" name="OC8: Justification"/>
-    <tableColumn id="29" name="OC9: Is the platform’s API documentation published in open access?&#10;This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication."/>
-    <tableColumn id="30" name="OC9: Justification"/>
-    <tableColumn id="31" name="OC10: Is the platform’s API documentation clearly written and exemplified?&#10;This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage."/>
-    <tableColumn id="32" name="OC10: Justification"/>
-    <tableColumn id="33" name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?&#10;This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access."/>
-    <tableColumn id="34" name="OC11: Justification"/>
-    <tableColumn id="35" name="OC12: Does the platform’s API documentation detail the response format of each endpoint?&#10;This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs."/>
-    <tableColumn id="36" name="OC12: Justification"/>
-    <tableColumn id="37" name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?&#10;This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages."/>
-    <tableColumn id="38" name="OC13: Justification"/>
-    <tableColumn id="39" name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?&#10;This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type."/>
-    <tableColumn id="40" name="OC14: Justification"/>
-    <tableColumn id="41" name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?&#10;This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. "/>
-    <tableColumn id="42" name="OC15: Justification"/>
-    <tableColumn id="43" name="OC16: Can data from a publication’s comments be extracted using the platform’s API?&#10;This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features."/>
-    <tableColumn id="44" name="OC16: Justification"/>
-    <tableColumn id="45" name="OC17: Can data from temporary content be extracted through the platform’s API?&#10;This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features."/>
-    <tableColumn id="46" name="OC17: Justification"/>
-    <tableColumn id="47" name="OC18: Can historical data be extracted through the platform’s API?&#10;This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved."/>
-    <tableColumn id="48" name="OC18: Justification"/>
-    <tableColumn id="49" name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?&#10;This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously."/>
-    <tableColumn id="50" name="OC19: Justification"/>
-    <tableColumn id="51" name="OC20: Are the results returned by the API consistently reproducible?&#10;This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly, including content that has been deleted between collections. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
-    <tableColumn id="52" name="OC20: Justification"/>
-    <tableColumn id="53" name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?&#10;This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
-    <tableColumn id="54" name="OC21: Justification"/>
-    <tableColumn id="55" name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?&#10;This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented."/>
-    <tableColumn id="56" name="OC22: Justification"/>
-    <tableColumn id="57" name="OC23: Does the platform’s API allow for filtering data based on publisher location?&#10;This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location."/>
-    <tableColumn id="58" name="OC23: Justification"/>
-    <tableColumn id="59" name="OC24: Does the platform’s API allow for filtering data based on content language?&#10;This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language."/>
-    <tableColumn id="60" name="OC24: Justification"/>
-    <tableColumn id="61" name="OC25: Does the platform’s API allow for filtering data by specific time periods?&#10;This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges."/>
-    <tableColumn id="62" name="OC25: Justification"/>
-    <tableColumn id="63" name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?&#10;This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data."/>
-    <tableColumn id="64" name="OC26: Justification"/>
+    <tableColumn name="Carimbo de data/hora" id="1"/>
+    <tableColumn name="Identification of analysts" id="2"/>
+    <tableColumn name="Which region is being analyzed?" id="3"/>
+    <tableColumn name="Which platform is being analyzed?" id="4"/>
+    <tableColumn name="SC1: Does the platform offer an API for collecting public user-generated content data?_x000a_This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration." id="5"/>
+    <tableColumn name="SC1: Justification" id="6"/>
+    <tableColumn name="SC2: Can the full scope of public content data be extracted through the platform’s API?_x000a_This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness." id="7"/>
+    <tableColumn name="SC2: Justification" id="8"/>
+    <tableColumn name="SC3: Is access to the platform’s API free of charge?_x000a_This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access." id="9"/>
+    <tableColumn name="SC3: Justification" id="10"/>
+    <tableColumn name="SC4: Does the platform offer a graphical interface for extracting data?_x000a_This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming." id="11"/>
+    <tableColumn name="SC4: Justification" id="12"/>
+    <tableColumn name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?_x000a_This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms." id="13"/>
+    <tableColumn name="OC1: Justification" id="14"/>
+    <tableColumn name="OC2: Can the requested data be extracted directly from the platform’s API response?_x000a_This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself." id="15"/>
+    <tableColumn name="OC2: Justification" id="16"/>
+    <tableColumn name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?_x000a_This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access." id="17"/>
+    <tableColumn name="OC3: Justification" id="18"/>
+    <tableColumn name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?_x000a_This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier." id="19"/>
+    <tableColumn name="OC4: Justification" id="20"/>
+    <tableColumn name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?_x000a_This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author." id="21"/>
+    <tableColumn name="OC5: Justification" id="22"/>
+    <tableColumn name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?_x000a_This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts." id="23"/>
+    <tableColumn name="OC6: Justification" id="24"/>
+    <tableColumn name="OC7: Does the API use locale-neutral data representations?_x000a_This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata." id="25"/>
+    <tableColumn name="OC7: Justification" id="26"/>
+    <tableColumn name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? _x000a_This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features." id="27"/>
+    <tableColumn name="OC8: Justification" id="28"/>
+    <tableColumn name="OC9: Is the platform’s API documentation published in open access?_x000a_This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication." id="29"/>
+    <tableColumn name="OC9: Justification" id="30"/>
+    <tableColumn name="OC10: Is the platform’s API documentation clearly written and exemplified?_x000a_This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage." id="31"/>
+    <tableColumn name="OC10: Justification" id="32"/>
+    <tableColumn name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?_x000a_This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access." id="33"/>
+    <tableColumn name="OC11: Justification" id="34"/>
+    <tableColumn name="OC12: Does the platform’s API documentation detail the response format of each endpoint?_x000a_This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs." id="35"/>
+    <tableColumn name="OC12: Justification" id="36"/>
+    <tableColumn name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?_x000a_This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages." id="37"/>
+    <tableColumn name="OC13: Justification" id="38"/>
+    <tableColumn name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?_x000a_This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type." id="39"/>
+    <tableColumn name="OC14: Justification" id="40"/>
+    <tableColumn name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?_x000a_This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. " id="41"/>
+    <tableColumn name="OC15: Justification" id="42"/>
+    <tableColumn name="OC16: Can data from a publication’s comments be extracted using the platform’s API?_x000a_This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features." id="43"/>
+    <tableColumn name="OC16: Justification" id="44"/>
+    <tableColumn name="OC17: Can data from temporary content be extracted through the platform’s API?_x000a_This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features." id="45"/>
+    <tableColumn name="OC17: Justification" id="46"/>
+    <tableColumn name="OC18: Can historical data be extracted through the platform’s API?_x000a_This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved." id="47"/>
+    <tableColumn name="OC18: Justification" id="48"/>
+    <tableColumn name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?_x000a_This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously." id="49"/>
+    <tableColumn name="OC19: Justification" id="50"/>
+    <tableColumn name="OC20: Are the results returned by the API consistently reproducible?_x000a_This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="51"/>
+    <tableColumn name="OC20: Justification" id="52"/>
+    <tableColumn name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?_x000a_This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="53"/>
+    <tableColumn name="OC21: Justification" id="54"/>
+    <tableColumn name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?_x000a_This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented." id="55"/>
+    <tableColumn name="OC22: Justification" id="56"/>
+    <tableColumn name="OC23: Does the platform’s API allow for filtering data based on publisher location?_x000a_This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location." id="57"/>
+    <tableColumn name="OC23: Justification" id="58"/>
+    <tableColumn name="OC24: Does the platform’s API allow for filtering data based on content language?_x000a_This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language." id="59"/>
+    <tableColumn name="OC24: Justification" id="60"/>
+    <tableColumn name="OC25: Does the platform’s API allow for filtering data by specific time periods?_x000a_This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges." id="61"/>
+    <tableColumn name="OC25: Justification" id="62"/>
+    <tableColumn name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?_x000a_This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data." id="63"/>
+    <tableColumn name="OC26: Justification" id="64"/>
   </tableColumns>
+  <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4285F4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="EA4335"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="FBBC04"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="34A853"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="FF6D01"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="46BDC6"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="1155CC"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="1155CC"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BR114"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="0" width="21.25"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="0" width="23.24"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="0" width="18.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="43.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="41.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="43.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="41.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="8.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="18.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="10.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="18.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="42.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="5.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="29.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="9.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="0" width="11.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="7.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="8.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="19.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="65" style="0" width="18.88"/>
+    <col customWidth="1" min="1" max="1" width="21.25"/>
+    <col customWidth="1" min="2" max="2" width="23.25"/>
+    <col customWidth="1" min="3" max="3" width="18.75"/>
+    <col customWidth="1" min="4" max="4" width="30.13"/>
+    <col customWidth="1" min="5" max="5" width="9.5"/>
+    <col customWidth="1" min="6" max="6" width="35.5"/>
+    <col customWidth="1" min="7" max="7" width="37.63"/>
+    <col customWidth="1" min="8" max="8" width="31.75"/>
+    <col customWidth="1" min="9" max="9" width="37.63"/>
+    <col customWidth="1" min="10" max="10" width="43.13"/>
+    <col customWidth="1" min="11" max="11" width="37.63"/>
+    <col customWidth="1" min="12" max="12" width="18.88"/>
+    <col customWidth="1" min="13" max="13" width="37.63"/>
+    <col customWidth="1" min="14" max="14" width="41.88"/>
+    <col customWidth="1" min="15" max="15" width="15.0"/>
+    <col customWidth="1" min="16" max="16" width="16.25"/>
+    <col customWidth="1" min="17" max="17" width="11.25"/>
+    <col customWidth="1" min="18" max="18" width="43.75"/>
+    <col customWidth="1" min="19" max="19" width="37.63"/>
+    <col customWidth="1" min="20" max="20" width="18.88"/>
+    <col customWidth="1" min="21" max="21" width="9.88"/>
+    <col customWidth="1" min="22" max="22" width="18.88"/>
+    <col customWidth="1" min="23" max="23" width="37.63"/>
+    <col customWidth="1" min="24" max="24" width="18.88"/>
+    <col customWidth="1" min="25" max="25" width="11.75"/>
+    <col customWidth="1" min="26" max="26" width="41.88"/>
+    <col customWidth="1" min="27" max="27" width="37.63"/>
+    <col customWidth="1" min="28" max="28" width="18.88"/>
+    <col customWidth="1" min="29" max="29" width="8.38"/>
+    <col customWidth="1" min="30" max="30" width="18.88"/>
+    <col customWidth="1" min="31" max="31" width="15.88"/>
+    <col customWidth="1" min="32" max="32" width="19.25"/>
+    <col customWidth="1" min="33" max="33" width="18.63"/>
+    <col customWidth="1" min="34" max="34" width="19.25"/>
+    <col customWidth="1" min="35" max="35" width="37.63"/>
+    <col customWidth="1" min="36" max="36" width="19.25"/>
+    <col customWidth="1" min="37" max="37" width="37.63"/>
+    <col customWidth="1" min="38" max="38" width="19.25"/>
+    <col customWidth="1" min="39" max="39" width="37.63"/>
+    <col customWidth="1" min="40" max="40" width="42.75"/>
+    <col customWidth="1" min="41" max="41" width="9.88"/>
+    <col customWidth="1" min="42" max="42" width="19.25"/>
+    <col customWidth="1" min="43" max="43" width="5.63"/>
+    <col customWidth="1" min="44" max="44" width="29.88"/>
+    <col customWidth="1" min="45" max="45" width="15.88"/>
+    <col customWidth="1" min="46" max="46" width="19.25"/>
+    <col customWidth="1" min="47" max="47" width="14.5"/>
+    <col customWidth="1" min="48" max="48" width="19.25"/>
+    <col customWidth="1" min="49" max="49" width="9.25"/>
+    <col customWidth="1" min="50" max="50" width="19.25"/>
+    <col customWidth="1" min="51" max="51" width="10.0"/>
+    <col customWidth="1" min="52" max="52" width="19.25"/>
+    <col customWidth="1" min="53" max="53" width="11.75"/>
+    <col customWidth="1" min="54" max="54" width="19.25"/>
+    <col customWidth="1" min="55" max="55" width="9.88"/>
+    <col customWidth="1" min="56" max="56" width="19.25"/>
+    <col customWidth="1" min="57" max="57" width="11.38"/>
+    <col customWidth="1" min="58" max="58" width="19.25"/>
+    <col customWidth="1" min="59" max="59" width="18.25"/>
+    <col customWidth="1" min="60" max="60" width="19.25"/>
+    <col customWidth="1" min="61" max="61" width="7.5"/>
+    <col customWidth="1" min="62" max="62" width="19.25"/>
+    <col customWidth="1" min="63" max="63" width="8.25"/>
+    <col customWidth="1" min="64" max="64" width="19.25"/>
+    <col customWidth="1" min="65" max="70" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,25 +1472,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1240,55 +1502,55 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
@@ -1300,37 +1562,37 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
@@ -1342,7 +1604,7 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AX1" s="1" t="s">
@@ -1354,37 +1616,37 @@
       <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" s="1" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="1" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="1" t="s">
@@ -1397,9 +1659,9 @@
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>45940.4170018287</v>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="4">
+        <v>45940.417001828704</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>64</v>
@@ -1597,9 +1859,9 @@
       <c r="BQ2" s="7"/>
       <c r="BR2" s="7"/>
     </row>
-    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>45940.4574845833</v>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>45940.457484583334</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>71</v>
@@ -1797,9 +2059,9 @@
       <c r="BQ3" s="7"/>
       <c r="BR3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>45940.4574845833</v>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>45940.457484583334</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>71</v>
@@ -1814,7 +2076,7 @@
         <v>66</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>66</v>
@@ -1997,198 +2259,198 @@
       <c r="BQ4" s="7"/>
       <c r="BR4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>45954.6752859144</v>
+    <row r="5" ht="159.0" customHeight="1">
+      <c r="A5" s="4">
+        <v>45954.67528591435</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>86</v>
+      <c r="L5" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA5" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="AF5" s="5" t="s">
-        <v>97</v>
+      <c r="AF5" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="AG5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AJ5" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR5" s="5" t="s">
         <v>103</v>
       </c>
+      <c r="AQ5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR5" s="9" t="s">
+        <v>104</v>
+      </c>
       <c r="AS5" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AU5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AW5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AX5" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AY5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ5" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BA5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BB5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BD5" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BE5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BG5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BK5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BL5" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BM5" s="7"/>
       <c r="BN5" s="7"/>
@@ -2197,198 +2459,198 @@
       <c r="BQ5" s="7"/>
       <c r="BR5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>45957.4241139005</v>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="4">
+        <v>45957.42411390046</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="L6" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="Q6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AQ6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AS6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AU6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AW6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BA6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BM6" s="7"/>
       <c r="BN6" s="7"/>
@@ -2397,198 +2659,198 @@
       <c r="BQ6" s="7"/>
       <c r="BR6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>45957.4284924537</v>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
+        <v>45957.428492453706</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="L7" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="W7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AA7" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AQ7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AS7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AU7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AW7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AY7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BA7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BM7" s="7"/>
       <c r="BN7" s="7"/>
@@ -2597,198 +2859,198 @@
       <c r="BQ7" s="7"/>
       <c r="BR7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>45957.432708287</v>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="4">
+        <v>45957.43270828704</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="L8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="Q8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA8" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AO8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AQ8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AS8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AU8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AW8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AY8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BA8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL8" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BM8" s="7"/>
       <c r="BN8" s="7"/>
@@ -2797,198 +3059,198 @@
       <c r="BQ8" s="7"/>
       <c r="BR8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>45960.6575131019</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="5" t="s">
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="11">
+        <v>45960.65751310185</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="E9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="G9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="5" t="s">
+      <c r="I9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="5" t="s">
+      <c r="K9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P9" s="5" t="s">
+      <c r="M9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA9" s="5" t="s">
+      <c r="O9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AB9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AE9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AI9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AM9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AO9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AS9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AU9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AW9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AY9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BA9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BC9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BE9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BG9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BI9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="BK9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL9" s="5" t="s">
-        <v>138</v>
+      <c r="AB9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AS9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AU9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AW9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BE9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BG9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BI9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BK9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL9" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="BM9" s="7"/>
       <c r="BN9" s="7"/>
@@ -2997,198 +3259,198 @@
       <c r="BQ9" s="7"/>
       <c r="BR9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>45961.4354872685</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="5" t="s">
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="11">
+        <v>45961.43548726852</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="D10" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="E10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="G10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="5" t="s">
+      <c r="I10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="O10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA10" s="5" t="s">
+      <c r="M10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA10" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AB10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AE10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AM10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AO10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AU10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AW10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="AY10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BC10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BE10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BG10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BI10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ10" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="BK10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL10" s="5" t="s">
-        <v>142</v>
+      <c r="AB10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AG10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AQ10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AW10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AY10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BA10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BC10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BG10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BI10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ10" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="BK10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL10" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="BM10" s="7"/>
       <c r="BN10" s="7"/>
@@ -3197,198 +3459,198 @@
       <c r="BQ10" s="7"/>
       <c r="BR10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>45961.6858838657</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="5" t="s">
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="11">
+        <v>45961.685883865735</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="E11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="G11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA11" s="5" t="s">
+      <c r="I11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA11" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AB11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AK11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AM11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AO11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AQ11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AS11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AU11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AW11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AY11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BC11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BG11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BI11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="BK11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL11" s="5" t="s">
-        <v>148</v>
+      <c r="AB11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AC11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AQ11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AS11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AW11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AY11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BC11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BG11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BI11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL11" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="BM11" s="7"/>
       <c r="BN11" s="7"/>
@@ -3397,198 +3659,198 @@
       <c r="BQ11" s="7"/>
       <c r="BR11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>45966.8209476273</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="5" t="s">
+    <row r="12" ht="249.75" customHeight="1">
+      <c r="A12" s="11">
+        <v>45966.82094762732</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="E12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="G12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="5" t="s">
+      <c r="I12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="R12" s="5" t="s">
+      <c r="K12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="S12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="T12" s="5" t="s">
+      <c r="O12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="R12" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="U12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="V12" s="5" t="s">
+      <c r="S12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="W12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="X12" s="5" t="s">
+      <c r="U12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="V12" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="Y12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z12" s="5" t="s">
+      <c r="W12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="AA12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB12" s="5" t="s">
+      <c r="Y12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z12" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AC12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD12" s="5" t="s">
+      <c r="AA12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB12" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="AE12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF12" s="5" t="s">
+      <c r="AC12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD12" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="AG12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH12" s="8" t="s">
+      <c r="AE12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF12" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="AI12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ12" s="5" t="s">
+      <c r="AG12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH12" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="AK12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL12" s="5" t="s">
+      <c r="AI12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ12" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="AM12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN12" s="5" t="s">
+      <c r="AK12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL12" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP12" s="5" t="s">
+      <c r="AM12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN12" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="AQ12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR12" s="5" t="s">
+      <c r="AO12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP12" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AS12" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT12" s="5" t="s">
+      <c r="AQ12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR12" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="AU12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV12" s="5" t="s">
+      <c r="AS12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT12" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AW12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX12" s="5" t="s">
+      <c r="AU12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV12" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AY12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ12" s="5" t="s">
+      <c r="AW12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX12" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="BA12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB12" s="5" t="s">
+      <c r="AY12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ12" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="BC12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD12" s="5" t="s">
+      <c r="BA12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB12" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="BE12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF12" s="5" t="s">
+      <c r="BC12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD12" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="BG12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH12" s="5" t="s">
+      <c r="BE12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF12" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="BI12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ12" s="5" t="s">
+      <c r="BG12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH12" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="BK12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BL12" s="5" t="s">
+      <c r="BI12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BJ12" s="9" t="s">
         <v>179</v>
+      </c>
+      <c r="BK12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL12" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
@@ -3597,198 +3859,198 @@
       <c r="BQ12" s="7"/>
       <c r="BR12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>45968.5244823264</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="5" t="s">
+    <row r="13" ht="151.5" customHeight="1">
+      <c r="A13" s="11">
+        <v>45968.52448232639</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="E13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="G13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="5" t="s">
+      <c r="I13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="O13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="R13" s="5" t="s">
+      <c r="K13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="S13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="T13" s="5" t="s">
+      <c r="O13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="R13" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="U13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="V13" s="5" t="s">
+      <c r="S13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="T13" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="W13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="X13" s="5" t="s">
+      <c r="U13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="V13" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="Y13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z13" s="5" t="s">
+      <c r="W13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="X13" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="AA13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB13" s="5" t="s">
+      <c r="Y13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="AC13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD13" s="5" t="s">
+      <c r="AA13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB13" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="AE13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF13" s="5" t="s">
+      <c r="AC13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD13" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="AG13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH13" s="5" t="s">
+      <c r="AE13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF13" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="AI13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ13" s="5" t="s">
+      <c r="AG13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH13" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="AK13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL13" s="5" t="s">
+      <c r="AI13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ13" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="AM13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN13" s="5" t="s">
+      <c r="AK13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL13" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP13" s="5" t="s">
+      <c r="AM13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN13" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="AQ13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR13" s="5" t="s">
+      <c r="AO13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP13" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="AS13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AT13" s="5" t="s">
+      <c r="AQ13" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR13" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="AU13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV13" s="5" t="s">
+      <c r="AS13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT13" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="AW13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX13" s="5" t="s">
+      <c r="AU13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV13" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="AY13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ13" s="5" t="s">
+      <c r="AW13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX13" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="BA13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BB13" s="5" t="s">
+      <c r="AY13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AZ13" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="BC13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BD13" s="5" t="s">
+      <c r="BA13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB13" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="BE13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF13" s="5" t="s">
+      <c r="BC13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD13" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="BG13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BH13" s="5" t="s">
+      <c r="BE13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF13" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="BI13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ13" s="5" t="s">
+      <c r="BG13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH13" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="BK13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BL13" s="5" t="s">
+      <c r="BI13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BJ13" s="9" t="s">
         <v>208</v>
+      </c>
+      <c r="BK13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL13" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="BM13" s="7"/>
       <c r="BN13" s="7"/>
@@ -3797,198 +4059,198 @@
       <c r="BQ13" s="7"/>
       <c r="BR13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="250.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>45971.7261773148</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    <row r="14" ht="250.5" customHeight="1">
+      <c r="A14" s="11">
+        <v>45971.72617731482</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="D14" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="E14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="G14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="5" t="s">
+      <c r="I14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="R14" s="5" t="s">
+      <c r="K14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="S14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="T14" s="5" t="s">
+      <c r="O14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="R14" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="U14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="V14" s="5" t="s">
+      <c r="S14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="T14" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="W14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="X14" s="5" t="s">
+      <c r="U14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="V14" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="Y14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z14" s="5" t="s">
+      <c r="W14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="X14" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="AA14" s="5" t="s">
+      <c r="Y14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z14" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA14" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AB14" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD14" s="5" t="s">
+      <c r="AB14" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="AE14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF14" s="5" t="s">
+      <c r="AC14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD14" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="AG14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH14" s="5" t="s">
+      <c r="AE14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF14" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="AI14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ14" s="5" t="s">
+      <c r="AG14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH14" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="AK14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL14" s="5" t="s">
+      <c r="AI14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ14" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="AM14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN14" s="5" t="s">
+      <c r="AK14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL14" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP14" s="5" t="s">
+      <c r="AM14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN14" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="AQ14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR14" s="5" t="s">
+      <c r="AO14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP14" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="AS14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AT14" s="5" t="s">
+      <c r="AQ14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR14" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="AU14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV14" s="5" t="s">
+      <c r="AS14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT14" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="AW14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AX14" s="5" t="s">
+      <c r="AU14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV14" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="AY14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ14" s="5" t="s">
+      <c r="AW14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX14" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="BA14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BB14" s="5" t="s">
+      <c r="AY14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ14" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="BC14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BD14" s="5" t="s">
+      <c r="BA14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB14" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="BE14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF14" s="5" t="s">
+      <c r="BC14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD14" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="BG14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH14" s="5" t="s">
+      <c r="BE14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF14" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="BI14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BJ14" s="5" t="s">
+      <c r="BG14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH14" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="BK14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="BL14" s="5" t="s">
+      <c r="BI14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BJ14" s="9" t="s">
         <v>237</v>
+      </c>
+      <c r="BK14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL14" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="BM14" s="7"/>
       <c r="BN14" s="7"/>
@@ -3997,7 +4259,7 @@
       <c r="BQ14" s="7"/>
       <c r="BR14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4069,7 +4331,7 @@
       <c r="BQ15" s="7"/>
       <c r="BR15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -4141,7 +4403,7 @@
       <c r="BQ16" s="7"/>
       <c r="BR16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -4213,7 +4475,7 @@
       <c r="BQ17" s="7"/>
       <c r="BR17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -4285,7 +4547,7 @@
       <c r="BQ18" s="7"/>
       <c r="BR18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4357,7 +4619,7 @@
       <c r="BQ19" s="7"/>
       <c r="BR19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -4429,7 +4691,7 @@
       <c r="BQ20" s="7"/>
       <c r="BR20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -4501,7 +4763,7 @@
       <c r="BQ21" s="7"/>
       <c r="BR21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -4573,7 +4835,7 @@
       <c r="BQ22" s="7"/>
       <c r="BR22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -4645,7 +4907,7 @@
       <c r="BQ23" s="7"/>
       <c r="BR23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -4717,7 +4979,7 @@
       <c r="BQ24" s="7"/>
       <c r="BR24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -4789,7 +5051,7 @@
       <c r="BQ25" s="7"/>
       <c r="BR25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -4861,7 +5123,7 @@
       <c r="BQ26" s="7"/>
       <c r="BR26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -4933,7 +5195,7 @@
       <c r="BQ27" s="7"/>
       <c r="BR27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -5005,7 +5267,7 @@
       <c r="BQ28" s="7"/>
       <c r="BR28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -5077,7 +5339,7 @@
       <c r="BQ29" s="7"/>
       <c r="BR29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -5149,7 +5411,7 @@
       <c r="BQ30" s="7"/>
       <c r="BR30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -5221,7 +5483,7 @@
       <c r="BQ31" s="7"/>
       <c r="BR31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -5293,7 +5555,7 @@
       <c r="BQ32" s="7"/>
       <c r="BR32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -5365,7 +5627,7 @@
       <c r="BQ33" s="7"/>
       <c r="BR33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -5437,7 +5699,7 @@
       <c r="BQ34" s="7"/>
       <c r="BR34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -5509,7 +5771,7 @@
       <c r="BQ35" s="7"/>
       <c r="BR35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -5581,7 +5843,7 @@
       <c r="BQ36" s="7"/>
       <c r="BR36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -5653,7 +5915,7 @@
       <c r="BQ37" s="7"/>
       <c r="BR37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -5725,7 +5987,7 @@
       <c r="BQ38" s="7"/>
       <c r="BR38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -5797,7 +6059,7 @@
       <c r="BQ39" s="7"/>
       <c r="BR39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -5869,7 +6131,7 @@
       <c r="BQ40" s="7"/>
       <c r="BR40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -5941,7 +6203,7 @@
       <c r="BQ41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -6013,7 +6275,7 @@
       <c r="BQ42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -6085,7 +6347,7 @@
       <c r="BQ43" s="7"/>
       <c r="BR43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6157,7 +6419,7 @@
       <c r="BQ44" s="7"/>
       <c r="BR44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -6229,7 +6491,7 @@
       <c r="BQ45" s="7"/>
       <c r="BR45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -6301,7 +6563,7 @@
       <c r="BQ46" s="7"/>
       <c r="BR46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -6373,7 +6635,7 @@
       <c r="BQ47" s="7"/>
       <c r="BR47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -6445,7 +6707,7 @@
       <c r="BQ48" s="7"/>
       <c r="BR48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6517,7 +6779,7 @@
       <c r="BQ49" s="7"/>
       <c r="BR49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -6589,7 +6851,7 @@
       <c r="BQ50" s="7"/>
       <c r="BR50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -6661,7 +6923,7 @@
       <c r="BQ51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -6733,7 +6995,7 @@
       <c r="BQ52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -6805,7 +7067,7 @@
       <c r="BQ53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -6877,7 +7139,7 @@
       <c r="BQ54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -6949,7 +7211,7 @@
       <c r="BQ55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -7021,7 +7283,7 @@
       <c r="BQ56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -7093,7 +7355,7 @@
       <c r="BQ57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -7165,7 +7427,7 @@
       <c r="BQ58" s="7"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -7237,7 +7499,7 @@
       <c r="BQ59" s="7"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -7309,7 +7571,7 @@
       <c r="BQ60" s="7"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -7381,7 +7643,7 @@
       <c r="BQ61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -7453,7 +7715,7 @@
       <c r="BQ62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -7525,7 +7787,7 @@
       <c r="BQ63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -7597,7 +7859,7 @@
       <c r="BQ64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -7669,7 +7931,7 @@
       <c r="BQ65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -7741,7 +8003,7 @@
       <c r="BQ66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -7813,7 +8075,7 @@
       <c r="BQ67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -7885,7 +8147,7 @@
       <c r="BQ68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -7957,7 +8219,7 @@
       <c r="BQ69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -8029,7 +8291,7 @@
       <c r="BQ70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -8101,7 +8363,7 @@
       <c r="BQ71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -8173,7 +8435,7 @@
       <c r="BQ72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -8245,7 +8507,7 @@
       <c r="BQ73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -8317,7 +8579,7 @@
       <c r="BQ74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -8389,7 +8651,7 @@
       <c r="BQ75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -8461,7 +8723,7 @@
       <c r="BQ76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -8533,7 +8795,7 @@
       <c r="BQ77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -8605,7 +8867,7 @@
       <c r="BQ78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -8677,7 +8939,7 @@
       <c r="BQ79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -8749,7 +9011,7 @@
       <c r="BQ80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -8821,7 +9083,7 @@
       <c r="BQ81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -8893,7 +9155,7 @@
       <c r="BQ82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -8965,7 +9227,7 @@
       <c r="BQ83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -9037,7 +9299,7 @@
       <c r="BQ84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -9109,7 +9371,7 @@
       <c r="BQ85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9181,7 +9443,7 @@
       <c r="BQ86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -9253,7 +9515,7 @@
       <c r="BQ87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -9325,7 +9587,7 @@
       <c r="BQ88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -9397,7 +9659,7 @@
       <c r="BQ89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -9469,7 +9731,7 @@
       <c r="BQ90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -9541,7 +9803,7 @@
       <c r="BQ91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -9613,7 +9875,7 @@
       <c r="BQ92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -9685,7 +9947,7 @@
       <c r="BQ93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -9757,7 +10019,7 @@
       <c r="BQ94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -9829,7 +10091,7 @@
       <c r="BQ95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -9901,7 +10163,7 @@
       <c r="BQ96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -9973,7 +10235,7 @@
       <c r="BQ97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -10045,7 +10307,7 @@
       <c r="BQ98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -10117,7 +10379,7 @@
       <c r="BQ99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -10189,7 +10451,7 @@
       <c r="BQ100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -10261,7 +10523,7 @@
       <c r="BQ101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -10333,7 +10595,7 @@
       <c r="BQ102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -10405,7 +10667,7 @@
       <c r="BQ103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -10477,7 +10739,7 @@
       <c r="BQ104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -10549,7 +10811,7 @@
       <c r="BQ105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -10621,7 +10883,7 @@
       <c r="BQ106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -10693,7 +10955,7 @@
       <c r="BQ107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -10765,7 +11027,7 @@
       <c r="BQ108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -10837,7 +11099,7 @@
       <c r="BQ109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -10909,7 +11171,7 @@
       <c r="BQ110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -10981,7 +11243,7 @@
       <c r="BQ111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -11053,7 +11315,7 @@
       <c r="BQ112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -11125,7 +11387,7 @@
       <c r="BQ113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -11199,22 +11461,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
-    <hyperlink ref="F4" r:id="rId2" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
-    <hyperlink ref="N5" r:id="rId3" display="This question is not applicable for Bluesky, because:&#10;* There is no specific authentication for researchers.&#10;* There is no private accounts or posts at Bluesky&#10;* There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.&#10;Source: &#10;&#10;https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb &#10;&#10;https://atproto.blue/en/latest/dm.html"/>
-    <hyperlink ref="AH5" r:id="rId4" display="Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only &quot;recomendations&quot; to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines"/>
-    <hyperlink ref="F11" r:id="rId5" display="Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for &quot;pins&quot; of the &quot;operation user_account&quot;. The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags"/>
-    <hyperlink ref="AH12" r:id="rId6" display="The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.&#10;https://developers.google.com/youtube/v3/docs &#10;https://developers.google.com/youtube/terms"/>
+    <hyperlink r:id="rId1" ref="F3"/>
+    <hyperlink r:id="rId2" ref="F4"/>
+    <hyperlink r:id="rId3" ref="N5"/>
+    <hyperlink r:id="rId4" ref="AH5"/>
+    <hyperlink r:id="rId5" ref="F11"/>
+    <hyperlink r:id="rId6" ref="AH12"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId7"/>
+  <drawing r:id="rId7"/>
+  <tableParts count="1">
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
+++ b/data/2025/xlsx_backups/UGC Framework (respostas).xlsx
@@ -1,375 +1,340 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Respostas ao formulário 1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$BL$14</definedName>
-  </definedNames>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="239">
-  <si>
-    <t>Carimbo de data/hora</t>
-  </si>
-  <si>
-    <t>Identification of analysts</t>
-  </si>
-  <si>
-    <t>Which region is being analyzed?</t>
-  </si>
-  <si>
-    <t>Which platform is being analyzed?</t>
-  </si>
-  <si>
-    <t>SC1: Does the platform offer an API for collecting public user-generated content data?
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="238">
+  <si>
+    <t xml:space="preserve">Carimbo de data/hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification of analysts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which region is being analyzed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which platform is being analyzed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC1: Does the platform offer an API for collecting public user-generated content data?
 This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration.</t>
   </si>
   <si>
-    <t>SC1: Justification</t>
-  </si>
-  <si>
-    <t>SC2: Can the full scope of public content data be extracted through the platform’s API?
+    <t xml:space="preserve">SC1: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC2: Can the full scope of public content data be extracted through the platform’s API?
 This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness.</t>
   </si>
   <si>
-    <t>SC2: Justification</t>
-  </si>
-  <si>
-    <t>SC3: Is access to the platform’s API free of charge?
+    <t xml:space="preserve">SC2: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3: Is access to the platform’s API free of charge?
 This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access.</t>
   </si>
   <si>
-    <t>SC3: Justification</t>
-  </si>
-  <si>
-    <t>SC4: Does the platform offer a graphical interface for extracting data?
+    <t xml:space="preserve">SC3: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC4: Does the platform offer a graphical interface for extracting data?
 This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming.</t>
   </si>
   <si>
-    <t>SC4: Justification</t>
-  </si>
-  <si>
-    <t>OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
+    <t xml:space="preserve">SC4: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?
 This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms.</t>
   </si>
   <si>
-    <t>OC1: Justification</t>
-  </si>
-  <si>
-    <t>OC2: Can the requested data be extracted directly from the platform’s API response?
+    <t xml:space="preserve">OC1: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC2: Can the requested data be extracted directly from the platform’s API response?
 This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself.</t>
   </si>
   <si>
-    <t>OC2: Justification</t>
-  </si>
-  <si>
-    <t>OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
+    <t xml:space="preserve">OC2: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?
 This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access.</t>
   </si>
   <si>
-    <t>OC3: Justification</t>
-  </si>
-  <si>
-    <t>OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
+    <t xml:space="preserve">OC3: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?
 This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier.</t>
   </si>
   <si>
-    <t>OC4: Justification</t>
-  </si>
-  <si>
-    <t>OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
+    <t xml:space="preserve">OC4: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?
 This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author.</t>
   </si>
   <si>
-    <t>OC5: Justification</t>
-  </si>
-  <si>
-    <t>OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
+    <t xml:space="preserve">OC5: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?
 This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts.</t>
   </si>
   <si>
-    <t>OC6: Justification</t>
-  </si>
-  <si>
-    <t>OC7: Does the API use locale-neutral data representations?
+    <t xml:space="preserve">OC6: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC7: Does the API use locale-neutral data representations?
 This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata.</t>
   </si>
   <si>
-    <t>OC7: Justification</t>
-  </si>
-  <si>
-    <t>OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
+    <t xml:space="preserve">OC7: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? 
 This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features.</t>
   </si>
   <si>
-    <t>OC8: Justification</t>
-  </si>
-  <si>
-    <t>OC9: Is the platform’s API documentation published in open access?
+    <t xml:space="preserve">OC8: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC9: Is the platform’s API documentation published in open access?
 This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication.</t>
   </si>
   <si>
-    <t>OC9: Justification</t>
-  </si>
-  <si>
-    <t>OC10: Is the platform’s API documentation clearly written and exemplified?
+    <t xml:space="preserve">OC9: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC10: Is the platform’s API documentation clearly written and exemplified?
 This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage.</t>
   </si>
   <si>
-    <t>OC10: Justification</t>
-  </si>
-  <si>
-    <t>OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
+    <t xml:space="preserve">OC10: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?
 This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access.</t>
   </si>
   <si>
-    <t>OC11: Justification</t>
-  </si>
-  <si>
-    <t>OC12: Does the platform’s API documentation detail the response format of each endpoint?
+    <t xml:space="preserve">OC11: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC12: Does the platform’s API documentation detail the response format of each endpoint?
 This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs.</t>
   </si>
   <si>
-    <t>OC12: Justification</t>
-  </si>
-  <si>
-    <t>OC13: Does the platform provide its API documentation in the official languages of the assessed region?
+    <t xml:space="preserve">OC12: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC13: Does the platform provide its API documentation in the official languages of the assessed region?
 This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages.</t>
   </si>
   <si>
-    <t>OC13: Justification</t>
-  </si>
-  <si>
-    <t>OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
+    <t xml:space="preserve">OC13: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?
 This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type.</t>
   </si>
   <si>
-    <t>OC14: Justification</t>
+    <t xml:space="preserve">OC14: Justification</t>
   </si>
   <si>
     <t xml:space="preserve">OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?
 This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. </t>
   </si>
   <si>
-    <t>OC15: Justification</t>
-  </si>
-  <si>
-    <t>OC16: Can data from a publication’s comments be extracted using the platform’s API?
+    <t xml:space="preserve">OC15: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC16: Can data from a publication’s comments be extracted using the platform’s API?
 This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features.</t>
   </si>
   <si>
-    <t>OC16: Justification</t>
-  </si>
-  <si>
-    <t>OC17: Can data from temporary content be extracted through the platform’s API?
+    <t xml:space="preserve">OC16: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC17: Can data from temporary content be extracted through the platform’s API?
 This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features.</t>
   </si>
   <si>
-    <t>OC17: Justification</t>
-  </si>
-  <si>
-    <t>OC18: Can historical data be extracted through the platform’s API?
+    <t xml:space="preserve">OC17: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC18: Can historical data be extracted through the platform’s API?
 This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved.</t>
   </si>
   <si>
-    <t>OC18: Justification</t>
-  </si>
-  <si>
-    <t>OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
+    <t xml:space="preserve">OC18: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?
 This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously.</t>
   </si>
   <si>
-    <t>OC19: Justification</t>
-  </si>
-  <si>
-    <t>OC20: Are the results returned by the API consistently reproducible?
+    <t xml:space="preserve">OC19: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC20: Are the results returned by the API consistently reproducible?
 This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
   </si>
   <si>
-    <t>OC20: Justification</t>
-  </si>
-  <si>
-    <t>OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
+    <t xml:space="preserve">OC20: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?
 This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals.</t>
   </si>
   <si>
-    <t>OC21: Justification</t>
-  </si>
-  <si>
-    <t>OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
+    <t xml:space="preserve">OC21: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?
 This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented.</t>
   </si>
   <si>
-    <t>OC22: Justification</t>
-  </si>
-  <si>
-    <t>OC23: Does the platform’s API allow for filtering data based on publisher location?
+    <t xml:space="preserve">OC22: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC23: Does the platform’s API allow for filtering data based on publisher location?
 This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location.</t>
   </si>
   <si>
-    <t>OC23: Justification</t>
-  </si>
-  <si>
-    <t>OC24: Does the platform’s API allow for filtering data based on content language?
+    <t xml:space="preserve">OC23: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC24: Does the platform’s API allow for filtering data based on content language?
 This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language.</t>
   </si>
   <si>
-    <t>OC24: Justification</t>
-  </si>
-  <si>
-    <t>OC25: Does the platform’s API allow for filtering data by specific time periods?
+    <t xml:space="preserve">OC24: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC25: Does the platform’s API allow for filtering data by specific time periods?
 This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges.</t>
   </si>
   <si>
-    <t>OC25: Justification</t>
-  </si>
-  <si>
-    <t>OC26: Can data from newly published content be extracted from the platform’s API in near real time?
+    <t xml:space="preserve">OC25: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OC26: Can data from newly published content be extracted from the platform’s API in near real time?
 This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data.</t>
   </si>
   <si>
-    <t>OC26: Justification</t>
-  </si>
-  <si>
-    <t>João Gabriel Haddad and Vinicius Branco</t>
-  </si>
-  <si>
-    <t>LinkedIn</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
-  </si>
-  <si>
-    <t>No or not applicable</t>
-  </si>
-  <si>
-    <t>Danielle Mello and João Gabriel Haddad</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
-https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
-    </r>
-  </si>
-  <si>
-    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
+    <t xml:space="preserve">OC26: Justification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Gabriel Haddad and Vinicius Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn only offers an API for collecting your own posts. The objective of the current API (Posts API) is to help business to manage their own pages and profiles. LinkedIn informs that this API is "restricted to organizations in which the authenticated member has one of the following company page roles: ADMINISTRATOR, DIRECT_SPONSORED_CONTENT_POSTER, CONTENT_ADMIN". Profiles also can "retrieve posts, comments, and likes on behalf of an authenticated member. [But] this permission is restricted and is available to approved users only". We conducted tests to confirm these limitations. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(SC1) LinkedIn only offers an API for collecting your own posts and does not offer a graphical interface for extracting data. https://web.archive.org/web/20251010121628/https://learn.microsoft.com/en-us/linkedin/marketing/community-management/shares/posts-api?view=li-lms-2025-09&amp;tabs=http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No or not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Mello and João Gabriel Haddad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t>Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. Moreover, the public content available is limited to a set of pages and profiles with a minimum number of followers or that has a verification badge.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
 https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
   </si>
   <si>
-    <t>Yes, but only for approved researchers</t>
-  </si>
-  <si>
-    <t>Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.
+    <t xml:space="preserve">Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage.
 https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
-    </r>
-  </si>
-  <si>
-    <t>João Haddad e Vinicius Scortegagna</t>
-  </si>
-  <si>
-    <t>Bluesky</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
+https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, but only for approved researchers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta offers Meta Content Library User Interface that allows approved researches to visualize and extract content generated by users on Facebook. This tool is more complete that what the API offers since it permits data extraction. https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Haddad e Vinicius Scortegagna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluesky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform offers an API for collecting all UGC data. , https://docs.bsky.app/docs/api/app-bsky-feed-get-posts and https://docs.bsky.app/docs/api/app-bsky-feed-get-author-feed</t>
   </si>
   <si>
     <t xml:space="preserve">All public content data can be extracted through the API. </t>
   </si>
   <si>
-    <t>The platforms requires only a BlueSky account to access the API</t>
-  </si>
-  <si>
-    <t>The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">This question is not applicable for Bluesky, because:
+    <t xml:space="preserve">The platforms requires only a BlueSky account to access the API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform does not provide a graphical interface for accessing or extracting public user-generated content data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This question is not applicable for Bluesky, because:
 * There is no specific authentication for researchers.
 * There is no private accounts or posts at Bluesky
 * There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.
 Source: 
 https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF434343"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://atproto.blue/en/latest/dm.html</t>
-    </r>
-  </si>
-  <si>
-    <t>Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
-  </si>
-  <si>
-    <t>Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
+https://atproto.blue/en/latest/dm.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responses to requests to the platform API provide the expected data in an appropriate format, without requiring redirection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actually, Bluesky does not requires tokens to use the API. Everything can be accessed easily only using standard login.</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an endpoint for extrating data from an individual publication. </t>
@@ -385,45 +350,35 @@
 </t>
   </si>
   <si>
-    <t>We did not find a change log in official API documentation, only reference for a change log from a developer</t>
-  </si>
-  <si>
-    <t>It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
-  </si>
-  <si>
-    <t>The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint. In its website, Bluesky makes reference to another documentation, related to its Python SDK. This documentation is clearly written and exemplified, however, we do not considered in our analisys because it was made by an independent developer</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://docs.bsky.app/docs/support/developer-guidelines</t>
-    </r>
-  </si>
-  <si>
-    <t>Although some endpoints lack explanation, there is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
-  </si>
-  <si>
-    <t>The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t>The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
-  </si>
-  <si>
-    <t>The Bluesky API only provides a way to a post author self-label the post content. 
+    <t xml:space="preserve">We did not find a change log in official API documentation, only reference for a change log from a developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is possible to access the documentation without registration or login. Source: https://docs.bsky.app/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bluesky's official API lacks explanation about its methods. For exemple, here: https://docs.bsky.app/docs/api/chat-bsky-convo-get-messages there is not explanation about this endpoint. In its website, Bluesky makes reference to another documentation, related to its Python SDK. This documentation is clearly written and exemplified, however, we do not considered in our analisys because it was made by an independent developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only "recomendations" to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although some endpoints lack explanation, there is response scheme for all endpoints in the documentation. Source: https://docs.bsky.app/docs/api/app-bsky-actor-get-profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The API documentation is available only in English. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform details the quota and rate limits in a specific page on the documentation. Source: https://docs.bsky.app/docs/get-started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bluesky API only provides a way to a post author self-label the post content. 
 * Check [SelfLabel definition](https://atproto.blue/en/latest/atproto/atproto_client.models.com.atproto.label.defs.html#atproto_client.models.com.atproto.label.defs.SelfLabel). However, there is no specific label for AI-generated content.</t>
   </si>
   <si>
-    <t>Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t>Bluesky does not have temporary content features.</t>
+    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, Bluesky does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluesky does not have temporary content features.</t>
   </si>
   <si>
     <t xml:space="preserve">It is possible to extract historical data through the API. </t>
@@ -453,139 +408,125 @@
     <t xml:space="preserve">Data can be extrated in near real time in Bluesky. </t>
   </si>
   <si>
-    <t>Fernando Ferreira &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>WhatsApp</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>TikTok</t>
-  </si>
-  <si>
-    <t>TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
-  </si>
-  <si>
-    <t>TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
-  </si>
-  <si>
-    <t>Rafael Tadeu &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>Kwai</t>
-  </si>
-  <si>
-    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t>Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>Danielle and Adriano</t>
-  </si>
-  <si>
-    <t>Snapchat</t>
-  </si>
-  <si>
-    <t>Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
+    <t xml:space="preserve">Fernando Ferreira &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Although Meta is expected to integrate public WhatsApp channels into the Meta Content Library in the near future, it had not done so by the time our analysis was conducted, and no specific timeframe has been announced. As a result, research on the platform still relies on data scraping (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Schaffner et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, WhatsApp likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhatsApp does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does offer research tools, but access is limited to researchers who are based in or affiliated with academic institutions in the United States, the European Economic Area, the United Kingdom, or Switzerland, as well as those affiliated with non-profit or independent research institutions, organizations, associations, or bodies within the European Union (TikTok, n.d.). As Brazil – and most of the world – fall outside this scope, researchers in other regions are limited to data scraping capabilities (Chemillier et al., 2022).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does not provide an API that enables programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions (TikTok, n.d.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions, TikTok likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok does not provide any form of access to or extraction of non-public user-generated content data for researchers based in Brazil or affiliated with Brazilian institutions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Tadeu &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. Only third-party, scraping-based APIs are available, which fall outside the scope of this work (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country (see Hale et al., 2024).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Kwai likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwai does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle and Adriano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapchat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapchat provides no public API for UGC extraction. The available API products (Snap Kit, Marketing API, Public Profile API, and Conversions API) serve primarily for marketing purposes and operate through allowlist-controlled partnerships. There is a set of Public Profile API endpoints that do not require profile owner authorization, but they provide access only to basic metadata and metrics for public profiles, not UGC.
 Source: https://developers.snap.com/api/home https://developers.snap.com/api/marketing-api/Public-Profile-API/GetStarted https://developers.snap.com/api/marketing-api/Public-Profile-API/CreatorDiscovery</t>
   </si>
   <si>
-    <t>Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t xml:space="preserve">Snap provides a dedicated program that allows approved academic researchers to request and obtain data through a formal process in accordance with the Digital Services Act (DSA). However, all vetting and application processes are handled by the national authority of EU Member States where the researcher is “based” or where the VLOP/VLOSE is established. Additionally, the purpose must be research on systemic risks in the EU. Therefore, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
+    <t xml:space="preserve">The platform offers free data access to vetted researchers in accordance with the Digital Services Act (DSA). The data catalog includes different types of content, such as public stories, comments, and public profile information. However, research conducted outside the European Union is generally not eligible to apply directly for access under the DSA research provisions.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
-  </si>
-  <si>
-    <t>The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
+    <t xml:space="preserve">Snapchat provides no official graphical user interface or tools for researchers to extract data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform offers free data access to vetted researchers under the DSA provisions, but only for public content.
 Source: https://values.snap.com/privacy/transparency/researcher-access</t>
   </si>
   <si>
-    <t>Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
-  </si>
-  <si>
-    <t>Felipe Grael &amp; Bruno Mattos</t>
-  </si>
-  <si>
-    <t>Discord</t>
-  </si>
-  <si>
-    <t>The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
-  </si>
-  <si>
-    <t>Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
-  </si>
-  <si>
-    <t>João Gabriel Haddad &amp; Vinícius Branco</t>
-  </si>
-  <si>
-    <t>Pinterest</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/</t>
-    </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve"> and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
-    </r>
-  </si>
-  <si>
-    <t>Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
-  </si>
-  <si>
-    <t>In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
-  </si>
-  <si>
-    <t>Adriano Belisario e Lucas Murakami</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
+    <t xml:space="preserve">Although the platform offers APIs, these are primarily designed for commercial and business integration purposes, rather than for open data access or research use. While Snapchat provides a formal data access program for vetted academic researchers under the DSA, this mechanism is strictly limited to studies on systemic risks within the European Union. There is no equivalent framework or public API enabling external researchers or the general public to access user-generated content or platform data for independent analysis outside the EU. Therefore, this criterion does not apply to the assessment of transparency and data access in the Brazilian context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe Grael &amp; Bruno Mattos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Discord API exists, but it is primarily designed for the development of bots and applications intended for specific servers (Discord, 2025). To integrate these bots, server administrators must authorize their inclusion and define which channels they can access and what permissions they are granted. Once authorized, a bot can interact with textual content, such as messages and channel metadata, according to the intents enabled for it (Discord, n.d.-a; n.d.-b). Because it is a highly permissioned system with restricted and pre-authorized access, the Discord API is not suited for transparency initiatives or systematic research on public interest data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Discord likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discord does not provide any form of access to or extraction of non-public user-generated content data, either in Brazil or in any other country.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Gabriel Haddad &amp; Vinícius Branco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for "pins" of the "operation user_account". The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the same way that it does not provide an API enabling programmatic access to or extraction of public user-generated content data, Pinterest likewise does not offer a graphical interface for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriano Belisario e Lucas Murakami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform does have an API (YouTube Data v3 API) that allows the extraction of public UGC. 
 https://developers.google.com/youtube/v3/docs.</t>
   </si>
   <si>
@@ -644,19 +585,9 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
+    <t xml:space="preserve">The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.
 https://developers.google.com/youtube/v3/docs 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://developers.google.com/youtube/terms</t>
-    </r>
+https://developers.google.com/youtube/terms</t>
   </si>
   <si>
     <t xml:space="preserve">Each method in the YouTube Data API v3 includes an example of its response format.
@@ -700,10 +631,10 @@
 </t>
   </si>
   <si>
-    <t>The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
-  </si>
-  <si>
-    <t>The documentation does not guarantee that API results are consistently reproducible and explicitly acknowledges approximations in key metrics. We made the same request to the search list endpoint multiple times, using “relevance” for the order parameter. The results differed in the order of the returned items.</t>
+    <t xml:space="preserve">The search list endpoint (for searching videos by query or channel ID) consumes 100 of the 10,000 daily points per request. Since each request can only return up to 50 videos, the maximum number of videos one can get by this method, per day, is 5,000. Therefore, if a monitoring task depends on search queries, this approach is insufficient to gather more than 5,000 publications per day. Also, there is a cap for the number of result pages retrieved for a set of parameters when using the search list endpoint. Our tests had to change parameters to get more data pages and hit the daily quota limit; otherwise, the collected video limit would be even lower if we were only allowed to use fixed parameters on this endpoint. However, the API's daily quota is sufficient to monitor more than 10,000 publications in 24 hours for other endpoints that do not depend on search (e.g., videos.list or playlistItems.list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The documentation does not guarantee that API results are consistently reproducible and explicitly acknowledges approximations in key metrics. We made the same request to the search list endpoint multiple times, using “relevance” for the order parameter. The results differed in the order of the returned items.</t>
   </si>
   <si>
     <t xml:space="preserve">There are frequent inconsistencies, even in collections using fixed parameters. In our tests, we found that the YouTube API does not necessarily honor user-defined filters. For instance, the documentation about the “relevanceLanguage” filter states that “results in other languages will still be returned if they are highly relevant to the search query term”, meaning the language filter operates as a soft preference rather than a strict constraint, allowing inconsistent results. In our tests, we confirmed that when requesting videos in Portuguese, one of the resulting items used English for its description and title. Also, comments were written in English. Although the video had no spoken dialogue —only images and English text —the previous statements already indicate that the video is targeted for English-speaking audiences. Recent academic studies have also addressed these consistency issues.
@@ -713,7 +644,7 @@
 </t>
   </si>
   <si>
-    <t>We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
+    <t xml:space="preserve">We ran tests comparing metrics from video and live streamings and confirmed that engagement metrics returned by the API are overall consistent with those on the user interface, although they are rounded and might not reflect the actual content available (e.g., total comment replies on the user interface can differ from the actual retrievable replies available via API). However, the API does not provide the metadata on AI-generated content, which is available through the web interface. Therefore, the data returned by the API does not correspond to the information displayed on the platform’s user interface at all levels of detail</t>
   </si>
   <si>
     <t xml:space="preserve">The API does not support filtering by channel/publisher location. This feature was deprecated from API v2. Currently, the “search.list” endpoint includes a location parameter, but this applies to video geographic metadata (where content was filmed), not channel/publisher location. The “regionCode” parameter "instructs the API to return search results for videos that can be viewed in the specified country", filtering by content availability region, not by publishers’ location.
@@ -736,94 +667,94 @@
 </t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
-  </si>
-  <si>
-    <t>Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
-  </si>
-  <si>
-    <t>In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
-  </si>
-  <si>
-    <t>X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
-  </si>
-  <si>
-    <t>If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
-  </si>
-  <si>
-    <t>The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
-  </si>
-  <si>
-    <t>Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
-  </si>
-  <si>
-    <t>For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
-  </si>
-  <si>
-    <t>The API documentation is available only in English (X, n.d.-l).</t>
-  </si>
-  <si>
-    <t>The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t>X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
-  </si>
-  <si>
-    <t>Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
-  </si>
-  <si>
-    <t>The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
-  </si>
-  <si>
-    <t>Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
-  </si>
-  <si>
-    <t>Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
-  </si>
-  <si>
-    <t>Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
-  </si>
-  <si>
-    <t>The platform returns data which matches the parameters and filters applied.</t>
-  </si>
-  <si>
-    <t>The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
-  </si>
-  <si>
-    <t>The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
-  </si>
-  <si>
-    <t>The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
-  </si>
-  <si>
-    <t>In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
-  </si>
-  <si>
-    <t>Telegram</t>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter provides a longstanding API (X, n.d.-l) that has been extensively documented and widely used for academic research (see Dongo et al., 2020). It remains accessible to anyone with a registered developer account, although, as will be discussed further, such access is now mostly paid (Mimizuka et al., 2025).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historically, X/Twitter has ensured that any public conversation published on the platform generates publicly available data that can be accessed and explored by developers through its API (Johnson, 2018).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In February 2023, X/Twitter announced that it would begin charging for the use of its API (Nóbrega, 2023), which had previously been mostly free of charge (Mimizuka et al., 2025). Currently, access to the API is divided into four levels: (i) Free, which allows retrieval of data from up to 100 posts per month; (ii) Basic, which, at a cost of USD 200 per month, allows retrieval of up to 15,000 posts; (iii) Pro, which, at a cost of USD 5,000 per month, allows retrieval of up to 1,000,000 posts; and (iv) Enterprise, for which pricing and usage limits are negotiated directly with the platform (X, n.d.-a). As the free plan offers extremely limited capabilities and is presented by the platform itself as a testing tier (X, n.d.-l), we do not consider it sufficient to characterize access to the platform’s API as free of charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter does not provide any form of access to or extraction of non-public user-generated content data in Brazil (X, n.d.-m).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If we consider only the limits of each tier, then tokens can be renewed without fear of data loss during extraction or monitoring. However, if we take into account the restrictions of the Basic Access tier – such as the 100-tweet monthly cap, the rate limit of 1 request every 15 minutes on the main tweet retrieval endpoint, and limited access to certain endpoints (e.g., GET /2/tweets/search/all is not available for Basic Access tier users) –, then the answer is no. Even if tokens are renewed, these tier-based restrictions tied to the app/user prevent continuous and comprehensive data collection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/:id endpoint enables the retrieval of comprehensive information about a single tweet, as identified by the provided ID (X, n.d.-c).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/users/:id/tweets endpoint enables the retrieval of comprehensive information about tweets made by a specific user, as identified by the provided ID (X, n.d.-d).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) endpoint enables the retrieval of comprehensive information about tweets published in the past seven days that match specific search terms, while the GET /2/tweets/search/all (X, n.d.-h) endpoint, available only to Pro and Enterprise API users, allows querying historical tweets dating back to the launch of the platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on a review of the X/Twitter API v2 documentation, the API employs largely locale-neutral representations for non-content metadata. Its structure and use of standardized formats ensure significant neutrality– for example, all timestamps (such as created_at) adhere to the ISO 8601 format and are returned in Coordinated Universal Time (UTC) (X, n.d.-k). Similarly, the lang field uses ISO 639-1 language codes, and country or regional codes follow standard ISO 3166-1 Alpha-2 conventions (X, n.d.-e).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation includes a dedicated section on migrating from API v1.1 to v2, outlining the key differences and new features. Although no deprecation timeline is provided, it states that v1.1 endpoints will remain functional but will no longer receive new features or updates (X, n.d.-f; n.d.-n).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation is publicly accessible to anyone (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation is comprehensive and includes all the necessary information, such as account-level limitations, permissions, detailed endpoint descriptions, and both current and upcoming features (X, n.d.-l). It also provides a well-structured migration guide from the previous version to the current one (X, n.d.-f).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation includes an extensive set of developer terms, collectively referred to as the “Developer Agreement and Policy” (X, n.d.-b).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each endpoint, the X/Twitter API documentation clearly describes the response format, specifying the structure of the returned JSON, the possible fields, their data types, and when they may or may not appear (X API Developers, n.d.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The API documentation is available only in English (X, n.d.-l).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API documentation clearly outlines the rate limits and quotas for each access tier, specifying how many requests can be made, within what time frame, and which resources or endpoints are affected (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X/Twitter does not allow content generated with the assistance of artificial intelligence to be labeled. Consequently, this type of information cannot be retrieved via the API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although it could be argued that replies and quotes serve this function, X/Twitter does not have dedicated comment features like other social media platforms analyzed in this study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API allows the retrieval of Spaces, live audio conversations that remain available for a limited period of time, through specific endpoints, either by known identifiers or by keywords (X, n.d.-j).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the GET /2/tweets/search/all (X, n.d.-h) endpoint allows querying historical tweets dating back to the launch of the platform, it is only available to Pro and Enterprise API users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although it is technically possible to monitor more than 10,000 posts in 24 hours using the X/Twitter API, the cost makes this impractical. The Basic Access tier, priced at USD 200 per month, allows retrieval of only 15,000 posts per month, which severely restricts large-scale monitoring, unless users opt for the Pro Access tier, which costs USD 5,000 per month (X, n.d.-a).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluding the seven-day limitation of the GET /2/tweets/search/recent endpoint (X, n.d.-i), data acquisitions using the X/Twitter API are consistently reproducible over time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The platform returns data which matches the parameters and filters applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The data extracted through the platform’s API reflects what is displayed on the user interface at the moment it is collected, meaning that key elements such as authorship, full content, interaction metrics, and referenced content are consistent with what users see on the interface.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X/Twitter API v2 documentation indicates that it is possible to filter data by publisher location using the profile_region field. However, this filter is not available to users or developers on the Basic Access tier. Therefore, we were unable to test or validate this functionality (X, n.d.-g).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i) and GET /2/tweets/search/all (X, n.d.-h) endpoints enable filtering of tweets according to content language through the use of the lang parameter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GET /2/tweets/search/recent (X, n.d.-i), though limited to the last seven days, and GET /2/tweets/search/all (X, n.d.-h) endpoints allow filtering of tweets based on specific timeframes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In our tests, we found that the delay between content appearing on the user interface and being accessible through the API was minimal, typically less than one hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telegram</t>
   </si>
   <si>
     <t xml:space="preserve">The platform offers an API that allows the collection of public data in Telegram conversations.
@@ -837,10 +768,10 @@
 </t>
   </si>
   <si>
-    <t>All Telegram APIs are free of charge: https://core.telegram.org/</t>
-  </si>
-  <si>
-    <t>Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
+    <t xml:space="preserve">All Telegram APIs are free of charge: https://core.telegram.org/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telegram does not provide any form of access to or extraction of non-public user-generated content data in Brazil.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram API access requires an access key that remains the same even after logging in multiple times. It will only change in specific situations, and the API provides the necessary methods to update it programmatically.
@@ -876,7 +807,7 @@
 </t>
   </si>
   <si>
-    <t>Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
+    <t xml:space="preserve">Telegram API documentation can be accessed without authentication. https://core.telegram.org/methods</t>
   </si>
   <si>
     <t xml:space="preserve">The Telegram and TDLib API documentation is not clearly written or exemplified. While it provides a technical reference of available classes and methods, it lacks detailed explanations and practical examples demonstrating how to call endpoints or implement typical workflows. The documentation’s structure assumes prior familiarity with Telegram’s internal architecture, making it difficult for developers to understand usage without relying on third-party resources or community libraries.
@@ -904,7 +835,7 @@
 </t>
   </si>
   <si>
-    <t>We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
+    <t xml:space="preserve">We found no official policy or technical specification for AI-generated content in Telegram’s API documentation and terms of service.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram allows extracting comments from channels with discussion features enabled. Each comment is treated as a reply within a message thread, which can be retrieved as structured data.
@@ -938,7 +869,7 @@
 </t>
   </si>
   <si>
-    <t>Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
+    <t xml:space="preserve">Telegram’s TDLib and core API do not provide any parameters or endpoints that allow filtering messages or posts by the publisher’s geographic location.</t>
   </si>
   <si>
     <t xml:space="preserve">Telegram’s TDLib and core API do not include any parameters or methods that enable filtering data based on the language of message content.
@@ -960,31 +891,48 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-      <name val="Roboto"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -992,474 +940,264 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FF3D3D3D"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
+          <fgColor rgb="FF0000FF"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Respostas ao formulário 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BL14" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$BL$14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BL14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:BL14"/>
   <tableColumns count="64">
-    <tableColumn name="Carimbo de data/hora" id="1"/>
-    <tableColumn name="Identification of analysts" id="2"/>
-    <tableColumn name="Which region is being analyzed?" id="3"/>
-    <tableColumn name="Which platform is being analyzed?" id="4"/>
-    <tableColumn name="SC1: Does the platform offer an API for collecting public user-generated content data?_x000a_This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration." id="5"/>
-    <tableColumn name="SC1: Justification" id="6"/>
-    <tableColumn name="SC2: Can the full scope of public content data be extracted through the platform’s API?_x000a_This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness." id="7"/>
-    <tableColumn name="SC2: Justification" id="8"/>
-    <tableColumn name="SC3: Is access to the platform’s API free of charge?_x000a_This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access." id="9"/>
-    <tableColumn name="SC3: Justification" id="10"/>
-    <tableColumn name="SC4: Does the platform offer a graphical interface for extracting data?_x000a_This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming." id="11"/>
-    <tableColumn name="SC4: Justification" id="12"/>
-    <tableColumn name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?_x000a_This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms." id="13"/>
-    <tableColumn name="OC1: Justification" id="14"/>
-    <tableColumn name="OC2: Can the requested data be extracted directly from the platform’s API response?_x000a_This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself." id="15"/>
-    <tableColumn name="OC2: Justification" id="16"/>
-    <tableColumn name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?_x000a_This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access." id="17"/>
-    <tableColumn name="OC3: Justification" id="18"/>
-    <tableColumn name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?_x000a_This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier." id="19"/>
-    <tableColumn name="OC4: Justification" id="20"/>
-    <tableColumn name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?_x000a_This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author." id="21"/>
-    <tableColumn name="OC5: Justification" id="22"/>
-    <tableColumn name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?_x000a_This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts." id="23"/>
-    <tableColumn name="OC6: Justification" id="24"/>
-    <tableColumn name="OC7: Does the API use locale-neutral data representations?_x000a_This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata." id="25"/>
-    <tableColumn name="OC7: Justification" id="26"/>
-    <tableColumn name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? _x000a_This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features." id="27"/>
-    <tableColumn name="OC8: Justification" id="28"/>
-    <tableColumn name="OC9: Is the platform’s API documentation published in open access?_x000a_This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication." id="29"/>
-    <tableColumn name="OC9: Justification" id="30"/>
-    <tableColumn name="OC10: Is the platform’s API documentation clearly written and exemplified?_x000a_This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage." id="31"/>
-    <tableColumn name="OC10: Justification" id="32"/>
-    <tableColumn name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?_x000a_This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access." id="33"/>
-    <tableColumn name="OC11: Justification" id="34"/>
-    <tableColumn name="OC12: Does the platform’s API documentation detail the response format of each endpoint?_x000a_This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs." id="35"/>
-    <tableColumn name="OC12: Justification" id="36"/>
-    <tableColumn name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?_x000a_This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages." id="37"/>
-    <tableColumn name="OC13: Justification" id="38"/>
-    <tableColumn name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?_x000a_This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type." id="39"/>
-    <tableColumn name="OC14: Justification" id="40"/>
-    <tableColumn name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?_x000a_This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. " id="41"/>
-    <tableColumn name="OC15: Justification" id="42"/>
-    <tableColumn name="OC16: Can data from a publication’s comments be extracted using the platform’s API?_x000a_This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features." id="43"/>
-    <tableColumn name="OC16: Justification" id="44"/>
-    <tableColumn name="OC17: Can data from temporary content be extracted through the platform’s API?_x000a_This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features." id="45"/>
-    <tableColumn name="OC17: Justification" id="46"/>
-    <tableColumn name="OC18: Can historical data be extracted through the platform’s API?_x000a_This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved." id="47"/>
-    <tableColumn name="OC18: Justification" id="48"/>
-    <tableColumn name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?_x000a_This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously." id="49"/>
-    <tableColumn name="OC19: Justification" id="50"/>
-    <tableColumn name="OC20: Are the results returned by the API consistently reproducible?_x000a_This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="51"/>
-    <tableColumn name="OC20: Justification" id="52"/>
-    <tableColumn name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?_x000a_This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals." id="53"/>
-    <tableColumn name="OC21: Justification" id="54"/>
-    <tableColumn name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?_x000a_This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented." id="55"/>
-    <tableColumn name="OC22: Justification" id="56"/>
-    <tableColumn name="OC23: Does the platform’s API allow for filtering data based on publisher location?_x000a_This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location." id="57"/>
-    <tableColumn name="OC23: Justification" id="58"/>
-    <tableColumn name="OC24: Does the platform’s API allow for filtering data based on content language?_x000a_This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language." id="59"/>
-    <tableColumn name="OC24: Justification" id="60"/>
-    <tableColumn name="OC25: Does the platform’s API allow for filtering data by specific time periods?_x000a_This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges." id="61"/>
-    <tableColumn name="OC25: Justification" id="62"/>
-    <tableColumn name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?_x000a_This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data." id="63"/>
-    <tableColumn name="OC26: Justification" id="64"/>
+    <tableColumn id="1" name="Carimbo de data/hora"/>
+    <tableColumn id="2" name="Identification of analysts"/>
+    <tableColumn id="3" name="Which region is being analyzed?"/>
+    <tableColumn id="4" name="Which platform is being analyzed?"/>
+    <tableColumn id="5" name="SC1: Does the platform offer an API for collecting public user-generated content data?&#10;This item verifies whether the platform provides an API with at least one endpoint for programmatically extracting public user-generated content to the users’ infrastructure. Public user-generated content is defined here as any publicly visible publication accessible by any platform user. The assessment should verify that the endpoint allows retrieval and storage of this content without requiring privileged or internal access beyond standard developer registration."/>
+    <tableColumn id="6" name="SC1: Justification"/>
+    <tableColumn id="7" name="SC2: Can the full scope of public content data be extracted through the platform’s API?&#10;This item verifies whether the platform enables programmatic discovery and extraction of data from the complete set of public user-generated content. The assessment should confirm that the API provides access to all types of public content on the platform, without exclusions or artificial restrictions that limit data completeness."/>
+    <tableColumn id="8" name="SC2: Justification"/>
+    <tableColumn id="9" name="SC3: Is access to the platform’s API free of charge?&#10;This item verifies whether API use is free of charge, since even modest fees can create barriers or force researchers in low-resourced settings to narrow the scope of their work. The assessment should verify the platform’s documentation and pricing policies to confirm that no fees are applied for API access."/>
+    <tableColumn id="10" name="SC3: Justification"/>
+    <tableColumn id="11" name="SC4: Does the platform offer a graphical interface for extracting data?&#10;This item verifies whether the platform offers a graphical interface for observing and collecting data to the users’ infrastructure. The data should be equivalent to that which is available through the API or the default user interface. The assessment should confirm the existence of an official tool, such as a dashboard or export feature, that allows extracting public content data without programming."/>
+    <tableColumn id="12" name="SC4: Justification"/>
+    <tableColumn id="13" name="OC1: Can researchers access non-public data (e.g., private groups, not direct messages)?&#10;This item verifies whether, beyond the retrieval and extraction of public user-generated content data, the API permits the extraction of any data from non-public content, such as posts and comments in private groups or discussion forums, subject to the implementation of adequate data hashing measures and specific researcher approval. The assessment should confirm that the API provides such access measures, either through specific endpoints or other controlled access mechanisms."/>
+    <tableColumn id="14" name="OC1: Justification"/>
+    <tableColumn id="15" name="OC2: Can the requested data be extracted directly from the platform’s API response?&#10;This item verifies whether the API returns structured data directly in its response, rather than only providing a redirect link to the data. Audiovisual media (e.g., images, videos, and audio) are excluded from this assessment. The assessment should check sample API responses to confirm that the requested public data is included in the returned payload itself."/>
+    <tableColumn id="16" name="OC2: Justification"/>
+    <tableColumn id="17" name="OC3: Does the platform’s API provide a form of authentication that allows for token renewal without the risk of data loss?&#10;This item verifies whether the tokens provided for API use can be renewed without risk of data loss, ensuring continuity and integrity of data monitoring and extraction. The assessment should check the platform’s documentation or directly observe the authentication and renewal process to confirm that token updates do not interrupt or compromise data access."/>
+    <tableColumn id="18" name="OC3: Justification"/>
+    <tableColumn id="19" name="OC4: Does the platform’s API offer an endpoint for extracting data from an individual publication?&#10;This item verifies whether it is possible to collect data from a specific public post on the platform using a unique identifier, rather than relying on search terms or other filters. The assessment should review the API documentation and test available endpoints to confirm that an individual publication can be retrieved directly by its unique identifier."/>
+    <tableColumn id="20" name="OC4: Justification"/>
+    <tableColumn id="21" name="OC5: Does the platform’s API offer an endpoint for extracting data from an individual author?&#10;This item verifies whether it is possible to collect data from public posts made by a specific author, using their username or unique identifier. The assessment should review the API documentation and test relevant endpoints to confirm that data can be retrieved directly for an individual author."/>
+    <tableColumn id="22" name="OC5: Justification"/>
+    <tableColumn id="23" name="OC6: Does the platform’s API provide an endpoint for extracting data based on search terms?&#10;This item verifies whether public user-generated content can be collected via individual or combined search terms, enabling the creation of datasets of posts mentioning those terms. The assessment should test search-related endpoints to confirm that queries using keywords return matching public posts."/>
+    <tableColumn id="24" name="OC6: Justification"/>
+    <tableColumn id="25" name="OC7: Does the API use locale-neutral data representations?&#10;This item verifies whether locale-sensitive data (e.g., timestamps, currency, numbers) are returned in a locale-neutral format, or whether relevant locale metadata is included when neutrality is not possible. The assessment should review the API documentation and inspect sample responses to confirm the presence of standardized formats or accompanying metadata."/>
+    <tableColumn id="26" name="OC7: Justification"/>
+    <tableColumn id="27" name="OC8: Does the platform implement a proper deprecation strategy to avoid breaking client applications while rolling out major changes in the API? &#10;This item verifies whether the platform’s documentation describes a deprecation strategy with a grace period before removing features. The assessment should review changelogs to confirm that deprecated features are listed with deprecation and removal dates and include migration instructions. This item applies only to breaking changes that require client updates, such as endpoint modifications, authentication updates, or the removal of features."/>
+    <tableColumn id="28" name="OC8: Justification"/>
+    <tableColumn id="29" name="OC9: Is the platform’s API documentation published in open access?&#10;This item verifies whether the platform makes its API documentation openly available on the internet, without requiring registration or login. The assessment should check whether full documentation can be accessed freely online without requiring account creation or authentication."/>
+    <tableColumn id="30" name="OC9: Justification"/>
+    <tableColumn id="31" name="OC10: Is the platform’s API documentation clearly written and exemplified?&#10;This item verifies whether the documentation for the platform’s API is clear, complete, and provides practical implementation examples. The assessment should review the documentation to confirm the presence of detailed explanations, structured references, and sample code or queries that illustrate correct usage."/>
+    <tableColumn id="32" name="OC10: Justification"/>
+    <tableColumn id="33" name="OC11: Does the platform clearly disclose the terms and conditions governing data access and exploration?&#10;This item verifies whether the platform provides explicit and accessible information outlining the legal, procedural, and technical conditions under which data can be accessed, queried, or explored. The assessment should review the documentation to confirm that it specifies the legal terms, the scope of accessible data, and any restrictions or obligations associated with responsible data access."/>
+    <tableColumn id="34" name="OC11: Justification"/>
+    <tableColumn id="35" name="OC12: Does the platform’s API documentation detail the response format of each endpoint?&#10;This item verifies whether the API documentation specifies the response format for each endpoint, including examples and potential error codes. The assessment should review the documentation to confirm that, in all or most cases, response structures are explicitly described and illustrated with sample outputs."/>
+    <tableColumn id="36" name="OC12: Justification"/>
+    <tableColumn id="37" name="OC13: Does the platform provide its API documentation in the official languages of the assessed region?&#10;This item verifies whether the platform provides its API documentation in the official languages of the assessed region. The assessment should review the documentation to confirm that complete and up-to-date versions are available in those languages."/>
+    <tableColumn id="38" name="OC13: Justification"/>
+    <tableColumn id="39" name="OC14: Does the platform’s API documentation detail the quota or rate limits applicable to each available endpoint?&#10;This item verifies whether the documentation specifies the limits for each endpoint. Rate limits define the maximum number of requests allowed within a given period (e.g., 1,000 requests per hour), while quotas set overall usage limits (e.g., total API calls per month). The assessment should review the documentation to confirm that usage limits are clearly stated, including variations by authentication level or endpoint type."/>
+    <tableColumn id="40" name="OC14: Justification"/>
+    <tableColumn id="41" name="OC15: Does the platform provide a way to label content that has been generated with artificial intelligence?&#10;This item verifies whether the platform automatically flags, or allows users to flag, AI-generated content, and whether this information is given in the API response. The assessment should review the documentation and test API outputs to confirm that these flags are included in the extracted data. "/>
+    <tableColumn id="42" name="OC15: Justification"/>
+    <tableColumn id="43" name="OC16: Can data from a publication’s comments be extracted using the platform’s API?&#10;This item verifies whether comment data, including their content, can be extracted when available on the platform, either together with publication data or with a dedicated endpoint. The assessment should test relevant endpoints to confirm that comments are retrievable as structured data. This item does not apply to platforms that do not have commenting features."/>
+    <tableColumn id="44" name="OC16: Justification"/>
+    <tableColumn id="45" name="OC17: Can data from temporary content be extracted through the platform’s API?&#10;This item verifies whether the platform’s API provides at least one endpoint for collecting data from temporary publications (e.g., stories, ephemeral messages). The assessment should test endpoints to confirm whether this type of short-lived content can be retrieved as structured data before it expires. This item does not apply to platforms that do not have temporary content features."/>
+    <tableColumn id="46" name="OC17: Justification"/>
+    <tableColumn id="47" name="OC18: Can historical data be extracted through the platform’s API?&#10;This item verifies whether the API provides endpoints that allow for a specified time range, going back more than one year from the time the request is made, to collect public user-generated content data. The assessment should test endpoints to confirm that historical data more than 12 months prior to the analysis can be retrieved."/>
+    <tableColumn id="48" name="OC18: Justification"/>
+    <tableColumn id="49" name="OC19: Is the number of requests allowed by the API sufficient for monitoring more than 10,000 publications in 24 hours?&#10;This item verifies whether data can be extracted without interruption and losses through the platform’s API for requests that accumulate more than 10,000 publications in 24 hours. The assessment should test the API to confirm that this volume of data can be collected continuously."/>
+    <tableColumn id="50" name="OC19: Justification"/>
+    <tableColumn id="51" name="OC20: Are the results returned by the API consistently reproducible?&#10;This item verifies whether data extracted via the platform’s API at any given time is consistent with other collections performed similarly. The assessment should conduct repeated test queries to confirm the reproducibility of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
+    <tableColumn id="52" name="OC20: Justification"/>
+    <tableColumn id="53" name="OC21: Is the data returned by the platform’s API consistent with the parameters and filters used in the request?&#10;This item verifies whether the data extracted through the API accurately reflects the parameters and filters specified in the request. The assessment should conduct repeated test queries to confirm the consistency of results or ground the response based on recent (less than 2 years) experiments published in peer-reviewed journals."/>
+    <tableColumn id="54" name="OC21: Justification"/>
+    <tableColumn id="55" name="OC22: Does the data extracted by the platform’s API reflect what is displayed on its user interface?&#10;This item verifies whether the data returned by the API corresponds to the information displayed on the platform’s user interface at all levels of detail. The assessment should compare API responses with the user interface to confirm that key elements, such as authorship, complete content, interaction counts (e.g., comments, shares, replies), and referenced content (e.g., shares, mentions), are fully represented."/>
+    <tableColumn id="56" name="OC22: Justification"/>
+    <tableColumn id="57" name="OC23: Does the platform’s API allow for filtering data based on publisher location?&#10;This item verifies whether the API supports applying location-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that data on public posts can be filtered by publisher location."/>
+    <tableColumn id="58" name="OC23: Justification"/>
+    <tableColumn id="59" name="OC24: Does the platform’s API allow for filtering data based on content language?&#10;This item verifies whether the API allows for applying language-based filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by content language."/>
+    <tableColumn id="60" name="OC24: Justification"/>
+    <tableColumn id="61" name="OC25: Does the platform’s API allow for filtering data by specific time periods?&#10;This item verifies whether the API allows applying temporal filters to data extraction. The assessment should test the endpoint for the main content type to confirm that public post data can be filtered by custom time ranges."/>
+    <tableColumn id="62" name="OC25: Justification"/>
+    <tableColumn id="63" name="OC26: Can data from newly published content be extracted from the platform’s API in near real time?&#10;This item verifies whether the API allows the collection of data from specific content within one hour of its publication. The assessment should test the endpoint for the main content type to confirm that it allows the ready extraction of recent public posts data."/>
+    <tableColumn id="64" name="OC26: Justification"/>
   </tableColumns>
-  <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4285F4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="EA4335"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="FBBC04"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="34A853"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="FF6D01"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="46BDC6"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="1155CC"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="1155CC"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:BR114"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.25"/>
-    <col customWidth="1" min="2" max="2" width="23.25"/>
-    <col customWidth="1" min="3" max="3" width="18.75"/>
-    <col customWidth="1" min="4" max="4" width="30.13"/>
-    <col customWidth="1" min="5" max="5" width="9.5"/>
-    <col customWidth="1" min="6" max="6" width="35.5"/>
-    <col customWidth="1" min="7" max="7" width="37.63"/>
-    <col customWidth="1" min="8" max="8" width="31.75"/>
-    <col customWidth="1" min="9" max="9" width="37.63"/>
-    <col customWidth="1" min="10" max="10" width="43.13"/>
-    <col customWidth="1" min="11" max="11" width="37.63"/>
-    <col customWidth="1" min="12" max="12" width="18.88"/>
-    <col customWidth="1" min="13" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="14" width="41.88"/>
-    <col customWidth="1" min="15" max="15" width="15.0"/>
-    <col customWidth="1" min="16" max="16" width="16.25"/>
-    <col customWidth="1" min="17" max="17" width="11.25"/>
-    <col customWidth="1" min="18" max="18" width="43.75"/>
-    <col customWidth="1" min="19" max="19" width="37.63"/>
-    <col customWidth="1" min="20" max="20" width="18.88"/>
-    <col customWidth="1" min="21" max="21" width="9.88"/>
-    <col customWidth="1" min="22" max="22" width="18.88"/>
-    <col customWidth="1" min="23" max="23" width="37.63"/>
-    <col customWidth="1" min="24" max="24" width="18.88"/>
-    <col customWidth="1" min="25" max="25" width="11.75"/>
-    <col customWidth="1" min="26" max="26" width="41.88"/>
-    <col customWidth="1" min="27" max="27" width="37.63"/>
-    <col customWidth="1" min="28" max="28" width="18.88"/>
-    <col customWidth="1" min="29" max="29" width="8.38"/>
-    <col customWidth="1" min="30" max="30" width="18.88"/>
-    <col customWidth="1" min="31" max="31" width="15.88"/>
-    <col customWidth="1" min="32" max="32" width="19.25"/>
-    <col customWidth="1" min="33" max="33" width="18.63"/>
-    <col customWidth="1" min="34" max="34" width="19.25"/>
-    <col customWidth="1" min="35" max="35" width="37.63"/>
-    <col customWidth="1" min="36" max="36" width="19.25"/>
-    <col customWidth="1" min="37" max="37" width="37.63"/>
-    <col customWidth="1" min="38" max="38" width="19.25"/>
-    <col customWidth="1" min="39" max="39" width="37.63"/>
-    <col customWidth="1" min="40" max="40" width="42.75"/>
-    <col customWidth="1" min="41" max="41" width="9.88"/>
-    <col customWidth="1" min="42" max="42" width="19.25"/>
-    <col customWidth="1" min="43" max="43" width="5.63"/>
-    <col customWidth="1" min="44" max="44" width="29.88"/>
-    <col customWidth="1" min="45" max="45" width="15.88"/>
-    <col customWidth="1" min="46" max="46" width="19.25"/>
-    <col customWidth="1" min="47" max="47" width="14.5"/>
-    <col customWidth="1" min="48" max="48" width="19.25"/>
-    <col customWidth="1" min="49" max="49" width="9.25"/>
-    <col customWidth="1" min="50" max="50" width="19.25"/>
-    <col customWidth="1" min="51" max="51" width="10.0"/>
-    <col customWidth="1" min="52" max="52" width="19.25"/>
-    <col customWidth="1" min="53" max="53" width="11.75"/>
-    <col customWidth="1" min="54" max="54" width="19.25"/>
-    <col customWidth="1" min="55" max="55" width="9.88"/>
-    <col customWidth="1" min="56" max="56" width="19.25"/>
-    <col customWidth="1" min="57" max="57" width="11.38"/>
-    <col customWidth="1" min="58" max="58" width="19.25"/>
-    <col customWidth="1" min="59" max="59" width="18.25"/>
-    <col customWidth="1" min="60" max="60" width="19.25"/>
-    <col customWidth="1" min="61" max="61" width="7.5"/>
-    <col customWidth="1" min="62" max="62" width="19.25"/>
-    <col customWidth="1" min="63" max="63" width="8.25"/>
-    <col customWidth="1" min="64" max="64" width="19.25"/>
-    <col customWidth="1" min="65" max="70" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="43.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="41.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="43.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="41.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="8.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="42.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="5.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="9.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="11.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="0" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="7.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="65" style="0" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,25 +1210,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1502,55 +1240,55 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
@@ -1562,37 +1300,37 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
@@ -1604,7 +1342,7 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
       <c r="AX1" s="1" t="s">
@@ -1616,37 +1354,37 @@
       <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="1" t="s">
@@ -1659,9 +1397,9 @@
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="4">
-        <v>45940.417001828704</v>
+    <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
+        <v>45940.4170018287</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>64</v>
@@ -1859,9 +1597,9 @@
       <c r="BQ2" s="7"/>
       <c r="BR2" s="7"/>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4">
-        <v>45940.457484583334</v>
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
+        <v>45940.4574845833</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>71</v>
@@ -2059,9 +1797,9 @@
       <c r="BQ3" s="7"/>
       <c r="BR3" s="7"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4">
-        <v>45940.457484583334</v>
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>45940.4574845833</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>71</v>
@@ -2076,7 +1814,7 @@
         <v>66</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>66</v>
@@ -2259,198 +1997,198 @@
       <c r="BQ4" s="7"/>
       <c r="BR4" s="7"/>
     </row>
-    <row r="5" ht="159.0" customHeight="1">
-      <c r="A5" s="4">
-        <v>45954.67528591435</v>
+    <row r="5" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>45954.6752859144</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="O5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="Q5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="U5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="W5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="W5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="X5" s="5" t="s">
+      <c r="Y5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z5" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="AA5" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="AC5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD5" s="5" t="s">
+      <c r="AE5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="AE5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF5" s="10" t="s">
+      <c r="AG5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH5" s="8" t="s">
+      <c r="AI5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="AI5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
+      <c r="AK5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL5" s="5" t="s">
+      <c r="AM5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="AM5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN5" s="5" t="s">
+      <c r="AO5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP5" s="5" t="s">
+      <c r="AQ5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="AQ5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR5" s="9" t="s">
+      <c r="AS5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="AS5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT5" s="5" t="s">
+      <c r="AU5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="AU5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV5" s="5" t="s">
+      <c r="AW5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AW5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX5" s="5" t="s">
+      <c r="AY5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AY5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ5" s="5" t="s">
+      <c r="BA5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="BA5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB5" s="5" t="s">
+      <c r="BC5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="BC5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD5" s="5" t="s">
+      <c r="BE5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="BE5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF5" s="5" t="s">
+      <c r="BG5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="BG5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH5" s="5" t="s">
+      <c r="BI5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="BI5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ5" s="5" t="s">
+      <c r="BK5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL5" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="BK5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL5" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="BM5" s="7"/>
       <c r="BN5" s="7"/>
@@ -2459,198 +2197,198 @@
       <c r="BQ5" s="7"/>
       <c r="BR5" s="7"/>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="4">
-        <v>45957.42411390046</v>
+    <row r="6" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>45957.4241139005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="O6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AQ6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AS6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AU6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AW6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AY6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BC6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BE6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BG6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BI6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BK6" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BM6" s="7"/>
       <c r="BN6" s="7"/>
@@ -2659,198 +2397,198 @@
       <c r="BQ6" s="7"/>
       <c r="BR6" s="7"/>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="4">
-        <v>45957.428492453706</v>
+    <row r="7" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>45957.4284924537</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="O7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AA7" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AM7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AO7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AQ7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AS7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AU7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AW7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AY7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BC7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BE7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BG7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BI7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BK7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BM7" s="7"/>
       <c r="BN7" s="7"/>
@@ -2859,198 +2597,198 @@
       <c r="BQ7" s="7"/>
       <c r="BR7" s="7"/>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="4">
-        <v>45957.43270828704</v>
+    <row r="8" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>45957.432708287</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="O8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="W8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="Z8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA8" s="5" t="s">
         <v>70</v>
       </c>
       <c r="AB8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AD8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AJ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AN8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AO8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AP8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AQ8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AR8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AS8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AT8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AU8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AV8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AW8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AX8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AY8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AZ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BA8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BB8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BC8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BD8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BE8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BF8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BG8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BH8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BI8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BJ8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BK8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BL8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BM8" s="7"/>
       <c r="BN8" s="7"/>
@@ -3059,198 +2797,198 @@
       <c r="BQ8" s="7"/>
       <c r="BR8" s="7"/>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="11">
-        <v>45960.65751310185</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="9" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>45960.6575131019</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="O9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA9" s="9" t="s">
+      <c r="Q9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AI9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AM9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AQ9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AS9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AU9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AW9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AY9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BA9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BC9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ9" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK9" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL9" s="9" t="s">
-        <v>139</v>
+      <c r="AB9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AQ9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AS9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AW9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BA9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL9" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="BM9" s="7"/>
       <c r="BN9" s="7"/>
@@ -3259,198 +2997,198 @@
       <c r="BQ9" s="7"/>
       <c r="BR9" s="7"/>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="11">
-        <v>45961.43548726852</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>45961.4354872685</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="M10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA10" s="9" t="s">
+      <c r="O10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AE10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AM10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AQ10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AS10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AU10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="AY10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BC10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BG10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BI10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="BK10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL10" s="9" t="s">
-        <v>143</v>
+      <c r="AB10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AQ10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AS10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AW10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AY10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BE10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BI10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BK10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL10" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="BM10" s="7"/>
       <c r="BN10" s="7"/>
@@ -3459,198 +3197,198 @@
       <c r="BQ10" s="7"/>
       <c r="BR10" s="7"/>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="11">
-        <v>45961.685883865735</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="11" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>45961.6858838657</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA11" s="9" t="s">
+      <c r="M11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="AB11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AG11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AS11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AW11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BA11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BC11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BG11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BI11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="BK11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BL11" s="9" t="s">
-        <v>149</v>
+      <c r="AB11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AS11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AW11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BC11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BE11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BG11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL11" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="BM11" s="7"/>
       <c r="BN11" s="7"/>
@@ -3659,198 +3397,198 @@
       <c r="BQ11" s="7"/>
       <c r="BR11" s="7"/>
     </row>
-    <row r="12" ht="249.75" customHeight="1">
-      <c r="A12" s="11">
-        <v>45966.82094762732</v>
-      </c>
-      <c r="B12" s="9" t="s">
+    <row r="12" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>45966.8209476273</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="9" t="s">
+      <c r="O12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="AC12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF12" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH12" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP12" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR12" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AS12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z12" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB12" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD12" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="AG12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH12" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="AI12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL12" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN12" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="AO12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="AQ12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR12" s="9" t="s">
+      <c r="AT12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AS12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT12" s="9" t="s">
+      <c r="AU12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV12" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="AU12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV12" s="9" t="s">
+      <c r="AW12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX12" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="AW12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX12" s="9" t="s">
+      <c r="AY12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ12" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="AY12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ12" s="9" t="s">
+      <c r="BA12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB12" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="BA12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BB12" s="9" t="s">
+      <c r="BC12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="BC12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BD12" s="9" t="s">
+      <c r="BE12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF12" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="BE12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF12" s="9" t="s">
+      <c r="BG12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH12" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="BG12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH12" s="9" t="s">
+      <c r="BI12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ12" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="BI12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ12" s="9" t="s">
+      <c r="BK12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL12" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="BK12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL12" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="BM12" s="7"/>
       <c r="BN12" s="7"/>
@@ -3859,198 +3597,198 @@
       <c r="BQ12" s="7"/>
       <c r="BR12" s="7"/>
     </row>
-    <row r="13" ht="151.5" customHeight="1">
-      <c r="A13" s="11">
-        <v>45968.52448232639</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="9" t="s">
+    <row r="13" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>45968.5244823264</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="9" t="s">
+      <c r="O13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="W13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="AM13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD13" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF13" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="AG13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH13" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ13" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL13" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN13" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="AO13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP13" s="9" t="s">
+      <c r="AR13" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="AQ13" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR13" s="9" t="s">
+      <c r="AS13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT13" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="AS13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT13" s="9" t="s">
+      <c r="AU13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV13" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="AU13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AV13" s="9" t="s">
+      <c r="AW13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX13" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="AW13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX13" s="9" t="s">
+      <c r="AY13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AZ13" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="AY13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ13" s="9" t="s">
+      <c r="BA13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB13" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="BA13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB13" s="9" t="s">
+      <c r="BC13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="BC13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD13" s="9" t="s">
+      <c r="BE13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF13" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="BE13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF13" s="9" t="s">
+      <c r="BG13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BH13" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="BG13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BH13" s="9" t="s">
+      <c r="BI13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ13" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="BI13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ13" s="9" t="s">
+      <c r="BK13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL13" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="BK13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL13" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="BM13" s="7"/>
       <c r="BN13" s="7"/>
@@ -4059,198 +3797,198 @@
       <c r="BQ13" s="7"/>
       <c r="BR13" s="7"/>
     </row>
-    <row r="14" ht="250.5" customHeight="1">
-      <c r="A14" s="11">
-        <v>45971.72617731482</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" s="9" t="s">
+    <row r="14" customFormat="false" ht="250.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>45971.7261773148</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="9" t="s">
+      <c r="I14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="R14" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="O14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="R14" s="9" t="s">
+      <c r="S14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="S14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="U14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="V14" s="9" t="s">
+      <c r="W14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="W14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="X14" s="9" t="s">
+      <c r="Y14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z14" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="Y14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z14" s="9" t="s">
+      <c r="AA14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB14" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="AA14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB14" s="9" t="s">
+      <c r="AC14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD14" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="AC14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD14" s="9" t="s">
+      <c r="AE14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF14" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AE14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF14" s="9" t="s">
+      <c r="AG14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH14" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="AG14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH14" s="9" t="s">
+      <c r="AI14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="AI14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ14" s="9" t="s">
+      <c r="AK14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL14" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="AK14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL14" s="9" t="s">
+      <c r="AM14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN14" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="AM14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN14" s="9" t="s">
+      <c r="AO14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP14" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="AO14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP14" s="9" t="s">
+      <c r="AQ14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR14" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="AQ14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR14" s="9" t="s">
+      <c r="AS14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT14" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="AS14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT14" s="9" t="s">
+      <c r="AU14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV14" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="AU14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV14" s="9" t="s">
+      <c r="AW14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AX14" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AW14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AX14" s="9" t="s">
+      <c r="AY14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ14" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="AY14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ14" s="9" t="s">
+      <c r="BA14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BB14" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="BA14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BB14" s="9" t="s">
+      <c r="BC14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD14" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="BC14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BD14" s="9" t="s">
+      <c r="BE14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF14" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="BE14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF14" s="9" t="s">
+      <c r="BG14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH14" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="BG14" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="BH14" s="9" t="s">
+      <c r="BI14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ14" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="BI14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ14" s="9" t="s">
+      <c r="BK14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="BL14" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="BK14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="BL14" s="9" t="s">
-        <v>238</v>
       </c>
       <c r="BM14" s="7"/>
       <c r="BN14" s="7"/>
@@ -4259,7 +3997,7 @@
       <c r="BQ14" s="7"/>
       <c r="BR14" s="7"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4331,7 +4069,7 @@
       <c r="BQ15" s="7"/>
       <c r="BR15" s="7"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -4403,7 +4141,7 @@
       <c r="BQ16" s="7"/>
       <c r="BR16" s="7"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -4475,7 +4213,7 @@
       <c r="BQ17" s="7"/>
       <c r="BR17" s="7"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -4547,7 +4285,7 @@
       <c r="BQ18" s="7"/>
       <c r="BR18" s="7"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4619,7 +4357,7 @@
       <c r="BQ19" s="7"/>
       <c r="BR19" s="7"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -4691,7 +4429,7 @@
       <c r="BQ20" s="7"/>
       <c r="BR20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -4763,7 +4501,7 @@
       <c r="BQ21" s="7"/>
       <c r="BR21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -4835,7 +4573,7 @@
       <c r="BQ22" s="7"/>
       <c r="BR22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -4907,7 +4645,7 @@
       <c r="BQ23" s="7"/>
       <c r="BR23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -4979,7 +4717,7 @@
       <c r="BQ24" s="7"/>
       <c r="BR24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -5051,7 +4789,7 @@
       <c r="BQ25" s="7"/>
       <c r="BR25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -5123,7 +4861,7 @@
       <c r="BQ26" s="7"/>
       <c r="BR26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -5195,7 +4933,7 @@
       <c r="BQ27" s="7"/>
       <c r="BR27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -5267,7 +5005,7 @@
       <c r="BQ28" s="7"/>
       <c r="BR28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -5339,7 +5077,7 @@
       <c r="BQ29" s="7"/>
       <c r="BR29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -5411,7 +5149,7 @@
       <c r="BQ30" s="7"/>
       <c r="BR30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -5483,7 +5221,7 @@
       <c r="BQ31" s="7"/>
       <c r="BR31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -5555,7 +5293,7 @@
       <c r="BQ32" s="7"/>
       <c r="BR32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -5627,7 +5365,7 @@
       <c r="BQ33" s="7"/>
       <c r="BR33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -5699,7 +5437,7 @@
       <c r="BQ34" s="7"/>
       <c r="BR34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -5771,7 +5509,7 @@
       <c r="BQ35" s="7"/>
       <c r="BR35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -5843,7 +5581,7 @@
       <c r="BQ36" s="7"/>
       <c r="BR36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -5915,7 +5653,7 @@
       <c r="BQ37" s="7"/>
       <c r="BR37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -5987,7 +5725,7 @@
       <c r="BQ38" s="7"/>
       <c r="BR38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -6059,7 +5797,7 @@
       <c r="BQ39" s="7"/>
       <c r="BR39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -6131,7 +5869,7 @@
       <c r="BQ40" s="7"/>
       <c r="BR40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -6203,7 +5941,7 @@
       <c r="BQ41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -6275,7 +6013,7 @@
       <c r="BQ42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -6347,7 +6085,7 @@
       <c r="BQ43" s="7"/>
       <c r="BR43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -6419,7 +6157,7 @@
       <c r="BQ44" s="7"/>
       <c r="BR44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -6491,7 +6229,7 @@
       <c r="BQ45" s="7"/>
       <c r="BR45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -6563,7 +6301,7 @@
       <c r="BQ46" s="7"/>
       <c r="BR46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -6635,7 +6373,7 @@
       <c r="BQ47" s="7"/>
       <c r="BR47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -6707,7 +6445,7 @@
       <c r="BQ48" s="7"/>
       <c r="BR48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6779,7 +6517,7 @@
       <c r="BQ49" s="7"/>
       <c r="BR49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -6851,7 +6589,7 @@
       <c r="BQ50" s="7"/>
       <c r="BR50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -6923,7 +6661,7 @@
       <c r="BQ51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -6995,7 +6733,7 @@
       <c r="BQ52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -7067,7 +6805,7 @@
       <c r="BQ53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -7139,7 +6877,7 @@
       <c r="BQ54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -7211,7 +6949,7 @@
       <c r="BQ55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -7283,7 +7021,7 @@
       <c r="BQ56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -7355,7 +7093,7 @@
       <c r="BQ57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -7427,7 +7165,7 @@
       <c r="BQ58" s="7"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -7499,7 +7237,7 @@
       <c r="BQ59" s="7"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -7571,7 +7309,7 @@
       <c r="BQ60" s="7"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -7643,7 +7381,7 @@
       <c r="BQ61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -7715,7 +7453,7 @@
       <c r="BQ62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -7787,7 +7525,7 @@
       <c r="BQ63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -7859,7 +7597,7 @@
       <c r="BQ64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -7931,7 +7669,7 @@
       <c r="BQ65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -8003,7 +7741,7 @@
       <c r="BQ66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -8075,7 +7813,7 @@
       <c r="BQ67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -8147,7 +7885,7 @@
       <c r="BQ68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -8219,7 +7957,7 @@
       <c r="BQ69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -8291,7 +8029,7 @@
       <c r="BQ70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -8363,7 +8101,7 @@
       <c r="BQ71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -8435,7 +8173,7 @@
       <c r="BQ72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -8507,7 +8245,7 @@
       <c r="BQ73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -8579,7 +8317,7 @@
       <c r="BQ74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -8651,7 +8389,7 @@
       <c r="BQ75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -8723,7 +8461,7 @@
       <c r="BQ76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -8795,7 +8533,7 @@
       <c r="BQ77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -8867,7 +8605,7 @@
       <c r="BQ78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -8939,7 +8677,7 @@
       <c r="BQ79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -9011,7 +8749,7 @@
       <c r="BQ80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -9083,7 +8821,7 @@
       <c r="BQ81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -9155,7 +8893,7 @@
       <c r="BQ82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -9227,7 +8965,7 @@
       <c r="BQ83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -9299,7 +9037,7 @@
       <c r="BQ84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -9371,7 +9109,7 @@
       <c r="BQ85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9443,7 +9181,7 @@
       <c r="BQ86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -9515,7 +9253,7 @@
       <c r="BQ87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -9587,7 +9325,7 @@
       <c r="BQ88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -9659,7 +9397,7 @@
       <c r="BQ89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -9731,7 +9469,7 @@
       <c r="BQ90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -9803,7 +9541,7 @@
       <c r="BQ91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -9875,7 +9613,7 @@
       <c r="BQ92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -9947,7 +9685,7 @@
       <c r="BQ93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -10019,7 +9757,7 @@
       <c r="BQ94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -10091,7 +9829,7 @@
       <c r="BQ95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -10163,7 +9901,7 @@
       <c r="BQ96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -10235,7 +9973,7 @@
       <c r="BQ97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -10307,7 +10045,7 @@
       <c r="BQ98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -10379,7 +10117,7 @@
       <c r="BQ99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -10451,7 +10189,7 @@
       <c r="BQ100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -10523,7 +10261,7 @@
       <c r="BQ101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -10595,7 +10333,7 @@
       <c r="BQ102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -10667,7 +10405,7 @@
       <c r="BQ103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -10739,7 +10477,7 @@
       <c r="BQ104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -10811,7 +10549,7 @@
       <c r="BQ105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -10883,7 +10621,7 @@
       <c r="BQ106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -10955,7 +10693,7 @@
       <c r="BQ107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -11027,7 +10765,7 @@
       <c r="BQ108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -11099,7 +10837,7 @@
       <c r="BQ109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -11171,7 +10909,7 @@
       <c r="BQ110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -11243,7 +10981,7 @@
       <c r="BQ111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -11315,7 +11053,7 @@
       <c r="BQ112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -11387,7 +11125,7 @@
       <c r="BQ113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -11461,16 +11199,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F3"/>
-    <hyperlink r:id="rId2" ref="F4"/>
-    <hyperlink r:id="rId3" ref="N5"/>
-    <hyperlink r:id="rId4" ref="AH5"/>
-    <hyperlink r:id="rId5" ref="F11"/>
-    <hyperlink r:id="rId6" ref="AH12"/>
+    <hyperlink ref="F3" r:id="rId1" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
+    <hyperlink ref="F4" r:id="rId2" display="Although Meta offers Meta Content Library API, extracting data is not allowed and violates the terms of usage. You can produce analysis and only the result of this analysis can by downloaded.&#10;https://web.archive.org/web/20251010131827/https://developers.facebook.com/docs/content-library-and-api&#10;https://web.archive.org/web/20251010132741/https://developers.facebook.com/docs/content-library-and-api/content-library-api/overview"/>
+    <hyperlink ref="N5" r:id="rId3" display="This question is not applicable for Bluesky, because:&#10;* There is no specific authentication for researchers.&#10;* There is no private accounts or posts at Bluesky&#10;* There are no private groups or discussion forums at Bluesky. There are only one-on-one messages on the platform and messages from the user can be retrieved using API.&#10;Source: &#10;&#10;https://github.com/NetLab-ECO-UFRJ/transparency-index/blob/main/2025/user-generated-content-framework/BR/br_bluesky.ipynb &#10;&#10;https://atproto.blue/en/latest/dm.html"/>
+    <hyperlink ref="AH5" r:id="rId4" display="Although Bluesky includes a link to its terms of use, it is not specific for API usage. There is also a Developer Guideline's page, but it includes only &quot;recomendations&quot; to developers. Sources: https://bsky.social/about/support/tos, https://bsky.social/about/support/privacy-policy, https://bsky.social/about/support/copyright, https://docs.bsky.app/docs/support/developer-guidelines"/>
+    <hyperlink ref="F11" r:id="rId5" display="Pinterest does not provide an API that enables programmatic access to or extraction of public user-generated content data, either in Brazil or in any other country. It only provides management for &quot;pins&quot; of the &quot;operation user_account&quot;. The only possible exception could be the /search/partner/pins endpoint, but it is still in beta and was not considered. Also, the documentation provides insufficient explanations about its behavior, but seems to be related to request for content from brand partnerships. Source: https://developers.pinterest.com/docs/api/v5/search_partner_pins, https://developers.pinterest.com/docs/key-concepts/using-beta-and-restricted-features/ and https://help.pinterest.com/en/business/article/approve-or-remove-paid-partnership-tags"/>
+    <hyperlink ref="AH12" r:id="rId6" display="The YouTube API documentation details its terms of use, including those specific to regions of the world. The document is linked at the bottom of the API documentation.&#10;https://developers.google.com/youtube/v3/docs &#10;https://developers.google.com/youtube/terms"/>
   </hyperlinks>
-  <drawing r:id="rId7"/>
-  <tableParts count="1">
-    <tablePart r:id="rId9"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>